--- a/Versão5/ARQ/Ontologia_Arquitetura.xlsx
+++ b/Versão5/ARQ/Ontologia_Arquitetura.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEA615F-5689-4D25-A356-69B37FCD3290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E8FA23-0C88-4A76-AB77-FA2B33973669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -6753,40 +6753,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
@@ -7139,6 +7105,22 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -7216,6 +7198,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7650,15 +7650,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="81.28515625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" style="47" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="1" width="10.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="81.3046875" style="26" customWidth="1"/>
+    <col min="3" max="3" width="4.3046875" style="47" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -7669,7 +7669,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -7726,7 +7726,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>54</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -7847,19 +7847,19 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="28">
         <f ca="1">NOW()</f>
-        <v>46258.59214641204</v>
+        <v>46264.563249884261</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>1328</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>1335</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>1332</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>1334</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>67</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>68</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>69</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="13" t="s">
         <v>70</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="13" t="s">
         <v>1325</v>
       </c>
@@ -7959,39 +7959,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A56445-53D9-475A-B2C6-D376FC6516D5}">
   <dimension ref="A1:AC351"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.42578125" style="70" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="139.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="122.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="131.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.28515625" style="86" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="75.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="25.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.69140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.53515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.3828125" style="70" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.53515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.69140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="139.15234375" style="26" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="122.53515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="131.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.3046875" style="86" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="75.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="25.69140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" style="26" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9" style="26" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.28515625" style="26"/>
+    <col min="30" max="16384" width="9.3046875" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="78" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="78" customFormat="1" ht="36.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="77">
         <v>1</v>
       </c>
@@ -8080,7 +8080,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -8177,7 +8177,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21">
         <v>5</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21">
         <v>6</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21">
         <v>7</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21">
         <v>8</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21">
         <v>9</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21">
         <v>11</v>
       </c>
@@ -9050,7 +9050,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21">
         <v>12</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21">
         <v>13</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21">
         <v>14</v>
       </c>
@@ -9341,7 +9341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="21">
         <v>15</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21">
         <v>16</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="21">
         <v>17</v>
       </c>
@@ -9632,7 +9632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="21">
         <v>18</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="21">
         <v>19</v>
       </c>
@@ -9826,7 +9826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="21">
         <v>20</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="21">
         <v>21</v>
       </c>
@@ -10020,7 +10020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="21">
         <v>22</v>
       </c>
@@ -10117,7 +10117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="21">
         <v>23</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="21">
         <v>24</v>
       </c>
@@ -10311,7 +10311,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="21">
         <v>25</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="21">
         <v>26</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="21">
         <v>27</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="21">
         <v>28</v>
       </c>
@@ -10699,7 +10699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="21">
         <v>29</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="21">
         <v>30</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="21">
         <v>31</v>
       </c>
@@ -10990,7 +10990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="21">
         <v>32</v>
       </c>
@@ -11087,7 +11087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="21">
         <v>33</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="21">
         <v>34</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="21">
         <v>35</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="21">
         <v>36</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="21">
         <v>37</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="21">
         <v>38</v>
       </c>
@@ -11669,7 +11669,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="21">
         <v>39</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="21">
         <v>40</v>
       </c>
@@ -11863,7 +11863,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="21">
         <v>41</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="21">
         <v>42</v>
       </c>
@@ -12057,7 +12057,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="21">
         <v>43</v>
       </c>
@@ -12154,7 +12154,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="21">
         <v>44</v>
       </c>
@@ -12251,7 +12251,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="21">
         <v>45</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="21">
         <v>46</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="21">
         <v>47</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="21">
         <v>48</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="21">
         <v>49</v>
       </c>
@@ -12736,7 +12736,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="21">
         <v>50</v>
       </c>
@@ -12833,7 +12833,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="21">
         <v>51</v>
       </c>
@@ -12930,7 +12930,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="21">
         <v>52</v>
       </c>
@@ -13027,7 +13027,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="21">
         <v>53</v>
       </c>
@@ -13124,7 +13124,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="21">
         <v>54</v>
       </c>
@@ -13221,7 +13221,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="21">
         <v>55</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="21">
         <v>56</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="21">
         <v>57</v>
       </c>
@@ -13512,7 +13512,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="21">
         <v>58</v>
       </c>
@@ -13609,7 +13609,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="21">
         <v>59</v>
       </c>
@@ -13706,7 +13706,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="21">
         <v>60</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="21">
         <v>61</v>
       </c>
@@ -13900,7 +13900,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="21">
         <v>62</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="21">
         <v>63</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="21">
         <v>64</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="21">
         <v>65</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="21">
         <v>66</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="21">
         <v>67</v>
       </c>
@@ -14482,7 +14482,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="21">
         <v>68</v>
       </c>
@@ -14579,7 +14579,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="21">
         <v>69</v>
       </c>
@@ -14676,7 +14676,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="21">
         <v>70</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="21">
         <v>71</v>
       </c>
@@ -14870,7 +14870,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="21">
         <v>72</v>
       </c>
@@ -14967,7 +14967,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="21">
         <v>73</v>
       </c>
@@ -15064,7 +15064,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="21">
         <v>74</v>
       </c>
@@ -15161,7 +15161,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="21">
         <v>75</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="21">
         <v>76</v>
       </c>
@@ -15355,7 +15355,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="21">
         <v>77</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="21">
         <v>78</v>
       </c>
@@ -15549,7 +15549,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="21">
         <v>79</v>
       </c>
@@ -15646,7 +15646,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="21">
         <v>80</v>
       </c>
@@ -15743,7 +15743,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="21">
         <v>81</v>
       </c>
@@ -15840,7 +15840,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="21">
         <v>82</v>
       </c>
@@ -15937,7 +15937,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="21">
         <v>83</v>
       </c>
@@ -16034,7 +16034,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="21">
         <v>84</v>
       </c>
@@ -16131,7 +16131,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="21">
         <v>85</v>
       </c>
@@ -16228,7 +16228,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="21">
         <v>86</v>
       </c>
@@ -16325,7 +16325,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="21">
         <v>87</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="21">
         <v>88</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="21">
         <v>89</v>
       </c>
@@ -16616,7 +16616,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="21">
         <v>90</v>
       </c>
@@ -16713,7 +16713,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="21">
         <v>91</v>
       </c>
@@ -16810,7 +16810,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="21">
         <v>92</v>
       </c>
@@ -16907,7 +16907,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="21">
         <v>93</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="21">
         <v>94</v>
       </c>
@@ -17101,7 +17101,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="21">
         <v>95</v>
       </c>
@@ -17198,7 +17198,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="21">
         <v>96</v>
       </c>
@@ -17295,7 +17295,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="21">
         <v>97</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="21">
         <v>98</v>
       </c>
@@ -17489,7 +17489,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="21">
         <v>99</v>
       </c>
@@ -17586,7 +17586,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="21">
         <v>100</v>
       </c>
@@ -17683,7 +17683,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="21">
         <v>101</v>
       </c>
@@ -17780,7 +17780,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="21">
         <v>102</v>
       </c>
@@ -17877,7 +17877,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="21">
         <v>103</v>
       </c>
@@ -17974,7 +17974,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="21">
         <v>104</v>
       </c>
@@ -18071,7 +18071,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="21">
         <v>105</v>
       </c>
@@ -18168,7 +18168,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="21">
         <v>106</v>
       </c>
@@ -18265,7 +18265,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="21">
         <v>107</v>
       </c>
@@ -18362,7 +18362,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="21">
         <v>108</v>
       </c>
@@ -18459,7 +18459,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="21">
         <v>109</v>
       </c>
@@ -18556,7 +18556,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="21">
         <v>110</v>
       </c>
@@ -18653,7 +18653,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="21">
         <v>111</v>
       </c>
@@ -18750,7 +18750,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="21">
         <v>112</v>
       </c>
@@ -18847,7 +18847,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="21">
         <v>113</v>
       </c>
@@ -18944,7 +18944,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="21">
         <v>114</v>
       </c>
@@ -19041,7 +19041,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="21">
         <v>115</v>
       </c>
@@ -19138,7 +19138,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="21">
         <v>116</v>
       </c>
@@ -19235,7 +19235,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="21">
         <v>117</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="21">
         <v>118</v>
       </c>
@@ -19429,7 +19429,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="21">
         <v>119</v>
       </c>
@@ -19526,7 +19526,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="21">
         <v>120</v>
       </c>
@@ -19623,7 +19623,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="21">
         <v>121</v>
       </c>
@@ -19720,7 +19720,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="21">
         <v>122</v>
       </c>
@@ -19817,7 +19817,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="21">
         <v>123</v>
       </c>
@@ -19914,7 +19914,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="21">
         <v>124</v>
       </c>
@@ -20011,7 +20011,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="21">
         <v>125</v>
       </c>
@@ -20108,7 +20108,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="21">
         <v>126</v>
       </c>
@@ -20205,7 +20205,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="21">
         <v>127</v>
       </c>
@@ -20302,7 +20302,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="21">
         <v>128</v>
       </c>
@@ -20399,7 +20399,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="21">
         <v>129</v>
       </c>
@@ -20496,7 +20496,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="21">
         <v>130</v>
       </c>
@@ -20593,7 +20593,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="21">
         <v>131</v>
       </c>
@@ -20690,7 +20690,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="21">
         <v>132</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="21">
         <v>133</v>
       </c>
@@ -20884,7 +20884,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="21">
         <v>134</v>
       </c>
@@ -20981,7 +20981,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="21">
         <v>135</v>
       </c>
@@ -21078,7 +21078,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="21">
         <v>136</v>
       </c>
@@ -21175,7 +21175,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="21">
         <v>137</v>
       </c>
@@ -21272,7 +21272,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="21">
         <v>138</v>
       </c>
@@ -21369,7 +21369,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="21">
         <v>139</v>
       </c>
@@ -21466,7 +21466,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="21">
         <v>140</v>
       </c>
@@ -21563,7 +21563,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="21">
         <v>141</v>
       </c>
@@ -21660,7 +21660,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="21">
         <v>142</v>
       </c>
@@ -21757,7 +21757,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="21">
         <v>143</v>
       </c>
@@ -21854,7 +21854,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="21">
         <v>144</v>
       </c>
@@ -21951,7 +21951,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="21">
         <v>145</v>
       </c>
@@ -22048,7 +22048,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="21">
         <v>146</v>
       </c>
@@ -22145,7 +22145,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="21">
         <v>147</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="21">
         <v>148</v>
       </c>
@@ -22339,7 +22339,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="21">
         <v>149</v>
       </c>
@@ -22436,7 +22436,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="21">
         <v>150</v>
       </c>
@@ -22533,7 +22533,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="21">
         <v>151</v>
       </c>
@@ -22630,7 +22630,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="21">
         <v>152</v>
       </c>
@@ -22727,7 +22727,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="21">
         <v>153</v>
       </c>
@@ -22824,7 +22824,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="154" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="21">
         <v>154</v>
       </c>
@@ -22921,7 +22921,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="155" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="21">
         <v>155</v>
       </c>
@@ -23018,7 +23018,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="156" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="21">
         <v>156</v>
       </c>
@@ -23115,7 +23115,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="157" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="21">
         <v>157</v>
       </c>
@@ -23212,7 +23212,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="158" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="21">
         <v>158</v>
       </c>
@@ -23309,7 +23309,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="159" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="21">
         <v>159</v>
       </c>
@@ -23406,7 +23406,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="160" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="21">
         <v>160</v>
       </c>
@@ -23503,7 +23503,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="161" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="21">
         <v>161</v>
       </c>
@@ -23600,7 +23600,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="162" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="21">
         <v>162</v>
       </c>
@@ -23697,7 +23697,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="163" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="21">
         <v>163</v>
       </c>
@@ -23794,7 +23794,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="164" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="21">
         <v>164</v>
       </c>
@@ -23891,7 +23891,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="165" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="21">
         <v>165</v>
       </c>
@@ -23988,7 +23988,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="166" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="21">
         <v>166</v>
       </c>
@@ -24085,7 +24085,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="167" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="21">
         <v>167</v>
       </c>
@@ -24182,7 +24182,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="168" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="21">
         <v>168</v>
       </c>
@@ -24279,7 +24279,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="169" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="21">
         <v>169</v>
       </c>
@@ -24376,7 +24376,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="170" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="21">
         <v>170</v>
       </c>
@@ -24473,7 +24473,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="171" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="21">
         <v>171</v>
       </c>
@@ -24570,7 +24570,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="172" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="21">
         <v>172</v>
       </c>
@@ -24667,7 +24667,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="173" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="21">
         <v>173</v>
       </c>
@@ -24764,7 +24764,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="174" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="21">
         <v>174</v>
       </c>
@@ -24861,7 +24861,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="175" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="21">
         <v>175</v>
       </c>
@@ -24958,7 +24958,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="176" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="21">
         <v>176</v>
       </c>
@@ -25055,7 +25055,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="177" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="21">
         <v>177</v>
       </c>
@@ -25152,7 +25152,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="178" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="21">
         <v>178</v>
       </c>
@@ -25249,7 +25249,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="179" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="21">
         <v>179</v>
       </c>
@@ -25346,7 +25346,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="180" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="21">
         <v>180</v>
       </c>
@@ -25443,7 +25443,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="181" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="21">
         <v>181</v>
       </c>
@@ -25540,7 +25540,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="182" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="21">
         <v>182</v>
       </c>
@@ -25637,7 +25637,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="183" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="21">
         <v>183</v>
       </c>
@@ -25734,7 +25734,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="184" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="21">
         <v>184</v>
       </c>
@@ -25831,7 +25831,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="185" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="21">
         <v>185</v>
       </c>
@@ -25928,7 +25928,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="186" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="21">
         <v>186</v>
       </c>
@@ -26025,7 +26025,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="187" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="21">
         <v>187</v>
       </c>
@@ -26122,7 +26122,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="188" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="21">
         <v>188</v>
       </c>
@@ -26219,7 +26219,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="189" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="21">
         <v>189</v>
       </c>
@@ -26316,7 +26316,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="190" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="21">
         <v>190</v>
       </c>
@@ -26413,7 +26413,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="191" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="21">
         <v>191</v>
       </c>
@@ -26510,7 +26510,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="192" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="21">
         <v>192</v>
       </c>
@@ -26607,7 +26607,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="193" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="21">
         <v>193</v>
       </c>
@@ -26704,7 +26704,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="194" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="21">
         <v>194</v>
       </c>
@@ -26801,7 +26801,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="195" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="21">
         <v>195</v>
       </c>
@@ -26898,7 +26898,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="196" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="21">
         <v>196</v>
       </c>
@@ -26995,7 +26995,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="197" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="21">
         <v>197</v>
       </c>
@@ -27092,7 +27092,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="198" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="21">
         <v>198</v>
       </c>
@@ -27189,7 +27189,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="199" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="21">
         <v>199</v>
       </c>
@@ -27286,7 +27286,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="200" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="21">
         <v>200</v>
       </c>
@@ -27383,7 +27383,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="201" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="21">
         <v>201</v>
       </c>
@@ -27480,7 +27480,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="202" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="21">
         <v>202</v>
       </c>
@@ -27577,7 +27577,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="203" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="21">
         <v>203</v>
       </c>
@@ -27674,7 +27674,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="204" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="21">
         <v>204</v>
       </c>
@@ -27771,7 +27771,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="205" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="21">
         <v>205</v>
       </c>
@@ -27868,7 +27868,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="206" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="21">
         <v>206</v>
       </c>
@@ -27965,7 +27965,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="207" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="21">
         <v>207</v>
       </c>
@@ -28062,7 +28062,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="208" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="21">
         <v>208</v>
       </c>
@@ -28159,7 +28159,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="209" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="21">
         <v>209</v>
       </c>
@@ -28256,7 +28256,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="210" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="21">
         <v>210</v>
       </c>
@@ -28353,7 +28353,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="211" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="21">
         <v>211</v>
       </c>
@@ -28450,7 +28450,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="212" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="21">
         <v>212</v>
       </c>
@@ -28547,7 +28547,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="213" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="21">
         <v>213</v>
       </c>
@@ -28644,7 +28644,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="214" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="21">
         <v>214</v>
       </c>
@@ -28741,7 +28741,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="215" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="21">
         <v>215</v>
       </c>
@@ -28838,7 +28838,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="216" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="21">
         <v>216</v>
       </c>
@@ -28935,7 +28935,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="217" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="21">
         <v>217</v>
       </c>
@@ -29032,7 +29032,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="218" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="21">
         <v>218</v>
       </c>
@@ -29129,7 +29129,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="219" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="21">
         <v>219</v>
       </c>
@@ -29226,7 +29226,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="220" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="21">
         <v>220</v>
       </c>
@@ -29323,7 +29323,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="221" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="21">
         <v>221</v>
       </c>
@@ -29420,7 +29420,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="222" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="21">
         <v>222</v>
       </c>
@@ -29517,7 +29517,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="223" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="21">
         <v>223</v>
       </c>
@@ -29614,7 +29614,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="224" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="21">
         <v>224</v>
       </c>
@@ -29711,7 +29711,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="225" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="21">
         <v>225</v>
       </c>
@@ -29808,7 +29808,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="226" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="21">
         <v>226</v>
       </c>
@@ -29905,7 +29905,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="227" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="21">
         <v>227</v>
       </c>
@@ -30002,7 +30002,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="228" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="21">
         <v>228</v>
       </c>
@@ -30099,7 +30099,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="229" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="21">
         <v>229</v>
       </c>
@@ -30196,7 +30196,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="230" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="21">
         <v>230</v>
       </c>
@@ -30293,7 +30293,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="231" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="21">
         <v>231</v>
       </c>
@@ -30390,7 +30390,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="232" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="21">
         <v>232</v>
       </c>
@@ -30487,7 +30487,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="233" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="21">
         <v>233</v>
       </c>
@@ -30584,7 +30584,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="234" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="21">
         <v>234</v>
       </c>
@@ -30681,7 +30681,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="235" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="21">
         <v>235</v>
       </c>
@@ -30778,7 +30778,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="236" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="21">
         <v>236</v>
       </c>
@@ -30875,7 +30875,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="237" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="21">
         <v>237</v>
       </c>
@@ -30972,7 +30972,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="238" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="21">
         <v>238</v>
       </c>
@@ -31069,7 +31069,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="239" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="21">
         <v>239</v>
       </c>
@@ -31166,7 +31166,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="240" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="21">
         <v>240</v>
       </c>
@@ -31263,7 +31263,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="241" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="21">
         <v>241</v>
       </c>
@@ -31360,7 +31360,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="242" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="21">
         <v>242</v>
       </c>
@@ -31457,7 +31457,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="243" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="21">
         <v>243</v>
       </c>
@@ -31554,7 +31554,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="244" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="21">
         <v>244</v>
       </c>
@@ -31651,7 +31651,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="245" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="21">
         <v>245</v>
       </c>
@@ -31748,7 +31748,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="246" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="21">
         <v>246</v>
       </c>
@@ -31845,7 +31845,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="247" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="21">
         <v>247</v>
       </c>
@@ -31942,7 +31942,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="248" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="21">
         <v>248</v>
       </c>
@@ -32039,7 +32039,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="249" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="21">
         <v>249</v>
       </c>
@@ -32136,7 +32136,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="250" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="21">
         <v>250</v>
       </c>
@@ -32233,7 +32233,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="251" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="21">
         <v>251</v>
       </c>
@@ -32330,7 +32330,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="252" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="21">
         <v>252</v>
       </c>
@@ -32427,7 +32427,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="253" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="21">
         <v>253</v>
       </c>
@@ -32524,7 +32524,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="254" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="21">
         <v>254</v>
       </c>
@@ -32621,7 +32621,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="255" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="21">
         <v>255</v>
       </c>
@@ -32718,7 +32718,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="256" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="21">
         <v>256</v>
       </c>
@@ -32815,7 +32815,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="257" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="21">
         <v>257</v>
       </c>
@@ -32912,7 +32912,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="258" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="21">
         <v>258</v>
       </c>
@@ -33009,7 +33009,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="259" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="21">
         <v>259</v>
       </c>
@@ -33106,7 +33106,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="260" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="21">
         <v>260</v>
       </c>
@@ -33203,7 +33203,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="261" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="21">
         <v>261</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="262" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="21">
         <v>262</v>
       </c>
@@ -33397,7 +33397,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="263" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="21">
         <v>263</v>
       </c>
@@ -33494,7 +33494,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="264" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="21">
         <v>264</v>
       </c>
@@ -33591,7 +33591,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="265" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="21">
         <v>265</v>
       </c>
@@ -33688,7 +33688,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="266" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="21">
         <v>266</v>
       </c>
@@ -33785,7 +33785,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="267" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="21">
         <v>267</v>
       </c>
@@ -33882,7 +33882,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="268" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="21">
         <v>268</v>
       </c>
@@ -33979,7 +33979,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="269" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="21">
         <v>269</v>
       </c>
@@ -34076,7 +34076,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="270" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="21">
         <v>270</v>
       </c>
@@ -34173,7 +34173,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="271" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="21">
         <v>271</v>
       </c>
@@ -34270,7 +34270,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="272" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="21">
         <v>272</v>
       </c>
@@ -34367,7 +34367,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="273" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="21">
         <v>273</v>
       </c>
@@ -34464,7 +34464,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="274" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="21">
         <v>274</v>
       </c>
@@ -34561,7 +34561,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="275" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="21">
         <v>275</v>
       </c>
@@ -34658,7 +34658,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="276" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="21">
         <v>276</v>
       </c>
@@ -34755,7 +34755,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="277" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="21">
         <v>277</v>
       </c>
@@ -34852,7 +34852,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="278" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="21">
         <v>278</v>
       </c>
@@ -34949,7 +34949,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="279" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="21">
         <v>279</v>
       </c>
@@ -35046,7 +35046,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="280" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="21">
         <v>280</v>
       </c>
@@ -35143,7 +35143,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="281" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="21">
         <v>281</v>
       </c>
@@ -35240,7 +35240,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="282" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="21">
         <v>282</v>
       </c>
@@ -35337,7 +35337,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="283" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="21">
         <v>283</v>
       </c>
@@ -35434,7 +35434,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="284" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="21">
         <v>284</v>
       </c>
@@ -35531,7 +35531,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="285" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="21">
         <v>285</v>
       </c>
@@ -35628,7 +35628,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="286" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="21">
         <v>286</v>
       </c>
@@ -35725,7 +35725,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="287" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="21">
         <v>287</v>
       </c>
@@ -35822,7 +35822,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="288" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="21">
         <v>288</v>
       </c>
@@ -35919,7 +35919,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="289" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="21">
         <v>289</v>
       </c>
@@ -36016,7 +36016,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="290" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="21">
         <v>290</v>
       </c>
@@ -36113,7 +36113,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="291" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="21">
         <v>291</v>
       </c>
@@ -36210,7 +36210,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="292" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="21">
         <v>292</v>
       </c>
@@ -36307,7 +36307,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="293" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="21">
         <v>293</v>
       </c>
@@ -36404,7 +36404,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="294" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="21">
         <v>294</v>
       </c>
@@ -36501,7 +36501,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="295" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="21">
         <v>295</v>
       </c>
@@ -36598,7 +36598,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="296" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="21">
         <v>296</v>
       </c>
@@ -36695,7 +36695,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="297" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="21">
         <v>297</v>
       </c>
@@ -36792,7 +36792,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="298" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="21">
         <v>298</v>
       </c>
@@ -36889,7 +36889,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="299" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="21">
         <v>299</v>
       </c>
@@ -36986,7 +36986,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="300" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A300" s="21">
         <v>300</v>
       </c>
@@ -37083,7 +37083,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="301" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="21">
         <v>301</v>
       </c>
@@ -37180,7 +37180,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="302" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A302" s="21">
         <v>302</v>
       </c>
@@ -37277,7 +37277,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="303" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A303" s="21">
         <v>303</v>
       </c>
@@ -37374,7 +37374,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="304" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="21">
         <v>304</v>
       </c>
@@ -37471,7 +37471,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="305" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A305" s="21">
         <v>305</v>
       </c>
@@ -37568,7 +37568,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="306" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A306" s="21">
         <v>306</v>
       </c>
@@ -37665,7 +37665,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="307" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A307" s="21">
         <v>307</v>
       </c>
@@ -37762,7 +37762,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="308" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A308" s="21">
         <v>308</v>
       </c>
@@ -37859,7 +37859,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="309" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A309" s="21">
         <v>309</v>
       </c>
@@ -37956,7 +37956,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="310" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A310" s="21">
         <v>310</v>
       </c>
@@ -38053,7 +38053,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="311" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A311" s="21">
         <v>311</v>
       </c>
@@ -38150,7 +38150,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="312" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A312" s="21">
         <v>312</v>
       </c>
@@ -38247,7 +38247,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="313" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A313" s="21">
         <v>313</v>
       </c>
@@ -38344,7 +38344,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="314" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A314" s="21">
         <v>314</v>
       </c>
@@ -38441,7 +38441,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="315" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A315" s="21">
         <v>315</v>
       </c>
@@ -38538,7 +38538,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="316" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A316" s="21">
         <v>316</v>
       </c>
@@ -38635,7 +38635,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="317" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A317" s="21">
         <v>317</v>
       </c>
@@ -38733,7 +38733,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="318" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A318" s="21">
         <v>318</v>
       </c>
@@ -38831,7 +38831,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="319" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A319" s="21">
         <v>319</v>
       </c>
@@ -38929,7 +38929,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="320" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A320" s="21">
         <v>320</v>
       </c>
@@ -39027,7 +39027,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="321" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A321" s="21">
         <v>321</v>
       </c>
@@ -39125,7 +39125,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="322" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A322" s="21">
         <v>322</v>
       </c>
@@ -39223,7 +39223,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="323" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A323" s="21">
         <v>323</v>
       </c>
@@ -39321,7 +39321,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="324" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A324" s="21">
         <v>324</v>
       </c>
@@ -39419,7 +39419,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="325" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A325" s="21">
         <v>325</v>
       </c>
@@ -39517,7 +39517,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="326" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A326" s="21">
         <v>326</v>
       </c>
@@ -39615,7 +39615,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="327" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A327" s="21">
         <v>327</v>
       </c>
@@ -39713,7 +39713,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="328" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A328" s="21">
         <v>328</v>
       </c>
@@ -39811,7 +39811,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="329" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A329" s="21">
         <v>329</v>
       </c>
@@ -39909,7 +39909,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="330" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A330" s="21">
         <v>330</v>
       </c>
@@ -40006,7 +40006,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="331" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A331" s="21">
         <v>331</v>
       </c>
@@ -40103,7 +40103,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="332" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A332" s="21">
         <v>332</v>
       </c>
@@ -40200,7 +40200,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="333" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A333" s="21">
         <v>333</v>
       </c>
@@ -40297,7 +40297,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="334" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A334" s="21">
         <v>334</v>
       </c>
@@ -40394,7 +40394,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="335" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A335" s="21">
         <v>335</v>
       </c>
@@ -40491,7 +40491,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="336" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A336" s="21">
         <v>336</v>
       </c>
@@ -40588,7 +40588,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="337" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A337" s="21">
         <v>337</v>
       </c>
@@ -40685,7 +40685,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="338" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A338" s="21">
         <v>338</v>
       </c>
@@ -40782,7 +40782,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="339" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A339" s="21">
         <v>339</v>
       </c>
@@ -40879,7 +40879,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="340" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A340" s="21">
         <v>340</v>
       </c>
@@ -40976,7 +40976,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="341" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A341" s="21">
         <v>341</v>
       </c>
@@ -41073,7 +41073,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="342" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A342" s="21">
         <v>342</v>
       </c>
@@ -41171,7 +41171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="343" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A343" s="21">
         <v>343</v>
       </c>
@@ -41269,7 +41269,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="344" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A344" s="21">
         <v>344</v>
       </c>
@@ -41367,7 +41367,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="345" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A345" s="21">
         <v>345</v>
       </c>
@@ -41465,7 +41465,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="346" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A346" s="21">
         <v>346</v>
       </c>
@@ -41563,7 +41563,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="347" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A347" s="21">
         <v>347</v>
       </c>
@@ -41661,7 +41661,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="348" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A348" s="21">
         <v>348</v>
       </c>
@@ -41759,7 +41759,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="349" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A349" s="21">
         <v>349</v>
       </c>
@@ -41857,7 +41857,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="350" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A350" s="21">
         <v>350</v>
       </c>
@@ -41955,7 +41955,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="351" spans="1:29" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:29" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="21">
         <v>351</v>
       </c>
@@ -41966,10 +41966,10 @@
         <v>2009</v>
       </c>
       <c r="D351" s="71" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E351" s="71" t="s">
         <v>2010</v>
-      </c>
-      <c r="E351" s="71" t="s">
-        <v>2011</v>
       </c>
       <c r="F351" s="71" t="s">
         <v>2012</v>
@@ -41995,11 +41995,11 @@
       </c>
       <c r="M351" s="24" t="str">
         <f t="shared" si="82"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N351" s="24" t="str">
         <f t="shared" si="82"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O351" s="24" t="str">
         <f t="shared" si="82"/>
@@ -42023,11 +42023,11 @@
       </c>
       <c r="U351" s="19" t="str">
         <f t="shared" si="77"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V351" s="25" t="str">
         <f t="shared" si="77"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W351" s="19" t="s">
         <v>81</v>
@@ -42057,53 +42057,53 @@
     <sortCondition ref="A1:A350"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A351:B351">
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F350 F352:F1048576">
-    <cfRule type="duplicateValues" dxfId="51" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17:F36">
-    <cfRule type="duplicateValues" dxfId="50" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F270">
-    <cfRule type="duplicateValues" dxfId="49" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F271:F272 F274:F279 F1:F16 F281:F350 F37:F269 F352:F1048576">
-    <cfRule type="duplicateValues" dxfId="48" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F271:F272 F274:F279 F281:F350 F1:F269 F352:F1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F273">
-    <cfRule type="duplicateValues" dxfId="46" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F280">
-    <cfRule type="duplicateValues" dxfId="45" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="540"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F351">
+    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F352:F1048576">
-    <cfRule type="duplicateValues" dxfId="44" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="667"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:X1 AA1:AA342 A1:F350 L1:R350 AD1:XFD350 T2:W350 AD352:XFD1048576 L352:X1048576 A352:F1048576 A351">
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
+  <conditionalFormatting sqref="R351">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S1:X1 AA1:AA342 A1:F350 L1:R350 AD1:XFD350 T2:W350 A352:F1048576 L352:X1048576 AD352:XFD1048576">
+    <cfRule type="cellIs" dxfId="40" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X352:X1048576 X1">
-    <cfRule type="duplicateValues" dxfId="43" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA344:AA350 AA352:AA1048576">
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B351">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F351">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R351">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42115,14 +42115,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.85546875" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.84375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="9" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="10"/>
-    <col min="11" max="16384" width="5.85546875" style="8"/>
+    <col min="1" max="1" width="2.53515625" style="9" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="10"/>
+    <col min="11" max="16384" width="5.84375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -42187,7 +42187,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -42254,7 +42254,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42269,15 +42269,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.69140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.15234375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.84375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12.3828125" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20">
         <v>0</v>
       </c>
@@ -42300,7 +42300,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -42326,15 +42326,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B2:G1048576">
-    <cfRule type="containsText" dxfId="40" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="38" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -42343,60 +42343,60 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A426B82-2E19-47C6-9DDF-914E7B26E6D0}">
   <dimension ref="A1:AW132"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.53515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3046875" style="42" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.84375" style="42" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4" style="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="72.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="72.69140625" style="26" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4" style="42" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="56.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="7.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="2.42578125" style="67" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="2.42578125" style="67" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="2.42578125" style="67" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="2.42578125" style="67" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="7.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.42578125" style="67" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="5.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="5.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="36.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="3.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="13.140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="7.140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="4.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="7.42578125" style="67" bestFit="1" customWidth="1"/>
-    <col min="50" max="16384" width="9.28515625" style="42"/>
+    <col min="13" max="13" width="56.3046875" style="42" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="7.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.15234375" style="67" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="2.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.15234375" style="67" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.3046875" style="42" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="2.3828125" style="67" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="2.3828125" style="67" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="2.3828125" style="67" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="7.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.3828125" style="67" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="2.3828125" style="67" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="5.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="36.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="3.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13.15234375" style="42" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="7.15234375" style="67" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="4.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="7.3828125" style="67" bestFit="1" customWidth="1"/>
+    <col min="50" max="16384" width="9.3046875" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="59" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" s="59" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="65" t="s">
         <v>10</v>
       </c>
@@ -42541,7 +42541,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="66">
         <v>2</v>
       </c>
@@ -42690,7 +42690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="66">
         <v>3</v>
       </c>
@@ -42839,7 +42839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="66">
         <v>4</v>
       </c>
@@ -42988,7 +42988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="66">
         <v>5</v>
       </c>
@@ -43137,7 +43137,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="66">
         <v>6</v>
       </c>
@@ -43286,7 +43286,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="66">
         <v>7</v>
       </c>
@@ -43435,7 +43435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="66">
         <v>8</v>
       </c>
@@ -43584,7 +43584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="66">
         <v>9</v>
       </c>
@@ -43733,7 +43733,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="66">
         <v>10</v>
       </c>
@@ -43882,7 +43882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="66">
         <v>11</v>
       </c>
@@ -44031,7 +44031,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="66">
         <v>12</v>
       </c>
@@ -44180,7 +44180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="66">
         <v>13</v>
       </c>
@@ -44329,7 +44329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="66">
         <v>14</v>
       </c>
@@ -44478,7 +44478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="66">
         <v>15</v>
       </c>
@@ -44627,7 +44627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="66">
         <v>16</v>
       </c>
@@ -44777,7 +44777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="66">
         <v>17</v>
       </c>
@@ -44927,7 +44927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="66">
         <v>18</v>
       </c>
@@ -45077,7 +45077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="66">
         <v>19</v>
       </c>
@@ -45227,7 +45227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="66">
         <v>20</v>
       </c>
@@ -45377,7 +45377,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="66">
         <v>21</v>
       </c>
@@ -45527,7 +45527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="66">
         <v>22</v>
       </c>
@@ -45677,7 +45677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="66">
         <v>23</v>
       </c>
@@ -45827,7 +45827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="66">
         <v>24</v>
       </c>
@@ -45977,7 +45977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="66">
         <v>25</v>
       </c>
@@ -46127,7 +46127,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="66">
         <v>26</v>
       </c>
@@ -46277,7 +46277,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="66">
         <v>27</v>
       </c>
@@ -46427,7 +46427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="66">
         <v>28</v>
       </c>
@@ -46577,7 +46577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="66">
         <v>29</v>
       </c>
@@ -46727,7 +46727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="66">
         <v>30</v>
       </c>
@@ -46877,7 +46877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="66">
         <v>31</v>
       </c>
@@ -47027,7 +47027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="66">
         <v>32</v>
       </c>
@@ -47176,7 +47176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="66">
         <v>33</v>
       </c>
@@ -47325,7 +47325,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="66">
         <v>34</v>
       </c>
@@ -47474,7 +47474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="66">
         <v>35</v>
       </c>
@@ -47623,7 +47623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="66">
         <v>36</v>
       </c>
@@ -47772,7 +47772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="66">
         <v>37</v>
       </c>
@@ -47921,7 +47921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="66">
         <v>38</v>
       </c>
@@ -48070,7 +48070,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="66">
         <v>39</v>
       </c>
@@ -48219,7 +48219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="66">
         <v>40</v>
       </c>
@@ -48368,7 +48368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="66">
         <v>41</v>
       </c>
@@ -48517,7 +48517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="66">
         <v>42</v>
       </c>
@@ -48666,7 +48666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="66">
         <v>43</v>
       </c>
@@ -48815,7 +48815,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="66">
         <v>44</v>
       </c>
@@ -48964,7 +48964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="66">
         <v>45</v>
       </c>
@@ -49113,7 +49113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="66">
         <v>46</v>
       </c>
@@ -49262,7 +49262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="66">
         <v>47</v>
       </c>
@@ -49411,7 +49411,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="66">
         <v>48</v>
       </c>
@@ -49560,7 +49560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="66">
         <v>49</v>
       </c>
@@ -49709,7 +49709,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="66">
         <v>50</v>
       </c>
@@ -49858,7 +49858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="66">
         <v>51</v>
       </c>
@@ -50007,7 +50007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="66">
         <v>52</v>
       </c>
@@ -50156,7 +50156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="66">
         <v>53</v>
       </c>
@@ -50305,7 +50305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="66">
         <v>54</v>
       </c>
@@ -50454,7 +50454,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="66">
         <v>55</v>
       </c>
@@ -50603,7 +50603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="66">
         <v>56</v>
       </c>
@@ -50752,7 +50752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="66">
         <v>57</v>
       </c>
@@ -50901,7 +50901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="66">
         <v>58</v>
       </c>
@@ -51050,7 +51050,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="66">
         <v>59</v>
       </c>
@@ -51199,7 +51199,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="66">
         <v>60</v>
       </c>
@@ -51348,7 +51348,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="66">
         <v>61</v>
       </c>
@@ -51497,7 +51497,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="66">
         <v>62</v>
       </c>
@@ -51646,7 +51646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="66">
         <v>63</v>
       </c>
@@ -51795,7 +51795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="66">
         <v>64</v>
       </c>
@@ -51944,7 +51944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="66">
         <v>65</v>
       </c>
@@ -52093,7 +52093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="66">
         <v>66</v>
       </c>
@@ -52242,7 +52242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="66">
         <v>67</v>
       </c>
@@ -52391,7 +52391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="66">
         <v>68</v>
       </c>
@@ -52540,7 +52540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="66">
         <v>69</v>
       </c>
@@ -52689,7 +52689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="66">
         <v>70</v>
       </c>
@@ -52838,7 +52838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="66">
         <v>71</v>
       </c>
@@ -52987,7 +52987,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="66">
         <v>72</v>
       </c>
@@ -53136,7 +53136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="66">
         <v>73</v>
       </c>
@@ -53285,7 +53285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="66">
         <v>74</v>
       </c>
@@ -53434,7 +53434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="66">
         <v>75</v>
       </c>
@@ -53583,7 +53583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="66">
         <v>76</v>
       </c>
@@ -53732,7 +53732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="66">
         <v>77</v>
       </c>
@@ -53881,7 +53881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="66">
         <v>78</v>
       </c>
@@ -54030,7 +54030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="66">
         <v>79</v>
       </c>
@@ -54179,7 +54179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="66">
         <v>80</v>
       </c>
@@ -54328,7 +54328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="66">
         <v>81</v>
       </c>
@@ -54477,7 +54477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="66">
         <v>82</v>
       </c>
@@ -54626,7 +54626,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="66">
         <v>83</v>
       </c>
@@ -54775,7 +54775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="66">
         <v>84</v>
       </c>
@@ -54924,7 +54924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="66">
         <v>85</v>
       </c>
@@ -55073,7 +55073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="66">
         <v>86</v>
       </c>
@@ -55222,7 +55222,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="66">
         <v>87</v>
       </c>
@@ -55371,7 +55371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="66">
         <v>88</v>
       </c>
@@ -55520,7 +55520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="66">
         <v>89</v>
       </c>
@@ -55669,7 +55669,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="66">
         <v>90</v>
       </c>
@@ -55818,7 +55818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="66">
         <v>91</v>
       </c>
@@ -55967,7 +55967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="66">
         <v>92</v>
       </c>
@@ -56116,7 +56116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="66">
         <v>93</v>
       </c>
@@ -56265,7 +56265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="66">
         <v>94</v>
       </c>
@@ -56414,7 +56414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="66">
         <v>95</v>
       </c>
@@ -56563,7 +56563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="66">
         <v>96</v>
       </c>
@@ -56712,7 +56712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="66">
         <v>97</v>
       </c>
@@ -56861,7 +56861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="66">
         <v>98</v>
       </c>
@@ -57010,7 +57010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="66">
         <v>99</v>
       </c>
@@ -57159,7 +57159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="66">
         <v>100</v>
       </c>
@@ -57308,7 +57308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="66">
         <v>101</v>
       </c>
@@ -57457,7 +57457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="66">
         <v>102</v>
       </c>
@@ -57606,7 +57606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="66">
         <v>103</v>
       </c>
@@ -57755,7 +57755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="66">
         <v>104</v>
       </c>
@@ -57904,7 +57904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="66">
         <v>105</v>
       </c>
@@ -58053,7 +58053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="66">
         <v>106</v>
       </c>
@@ -58202,7 +58202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="66">
         <v>107</v>
       </c>
@@ -58351,7 +58351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="66">
         <v>108</v>
       </c>
@@ -58500,7 +58500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="66">
         <v>109</v>
       </c>
@@ -58649,7 +58649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="66">
         <v>110</v>
       </c>
@@ -58798,7 +58798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="66">
         <v>111</v>
       </c>
@@ -58947,7 +58947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="66">
         <v>112</v>
       </c>
@@ -59096,7 +59096,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="66">
         <v>113</v>
       </c>
@@ -59245,7 +59245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="66">
         <v>114</v>
       </c>
@@ -59394,7 +59394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="66">
         <v>115</v>
       </c>
@@ -59543,7 +59543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="66">
         <v>116</v>
       </c>
@@ -59692,7 +59692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="66">
         <v>117</v>
       </c>
@@ -59841,7 +59841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="66">
         <v>118</v>
       </c>
@@ -59990,7 +59990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="66">
         <v>119</v>
       </c>
@@ -60139,7 +60139,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="66">
         <v>120</v>
       </c>
@@ -60288,7 +60288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="66">
         <v>121</v>
       </c>
@@ -60437,7 +60437,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="66">
         <v>122</v>
       </c>
@@ -60586,7 +60586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="66">
         <v>123</v>
       </c>
@@ -60735,7 +60735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:49" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="66">
         <v>124</v>
       </c>
@@ -60884,7 +60884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:49" s="60" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:49" s="60" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="66">
         <v>125</v>
       </c>
@@ -61033,7 +61033,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="126" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="66">
         <v>126</v>
       </c>
@@ -61182,7 +61182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="66">
         <v>127</v>
       </c>
@@ -61331,7 +61331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="66">
         <v>128</v>
       </c>
@@ -61480,7 +61480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:49" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="66">
         <v>129</v>
       </c>
@@ -61629,7 +61629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="66">
         <v>130</v>
       </c>
@@ -61778,7 +61778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="66">
         <v>131</v>
       </c>
@@ -61927,7 +61927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:49" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="66">
         <v>132</v>
       </c>
@@ -62079,106 +62079,106 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1 B2:B31 B113:B132 A133:B1048576 D1:I1048576 L1:XFD124 A2:A132 T125:AO125 T126:XFD126 T127:AS127 AT127:XFD129 T128:AP129 AR128:AS129 T130:XFD131 L132:XFD1048576">
-    <cfRule type="cellIs" dxfId="37" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="88" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B31 B113:B1048576">
-    <cfRule type="duplicateValues" dxfId="36" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="35" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:B57">
-    <cfRule type="cellIs" dxfId="34" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="82" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B66">
-    <cfRule type="duplicateValues" dxfId="32" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B112">
-    <cfRule type="cellIs" dxfId="31" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="75" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67:B74">
-    <cfRule type="duplicateValues" dxfId="30" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75:B86">
-    <cfRule type="duplicateValues" dxfId="29" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75:B112">
-    <cfRule type="duplicateValues" dxfId="28" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="27" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130:B1048576 B113:B124">
-    <cfRule type="duplicateValues" dxfId="26" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C31">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C86">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C126">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C127">
-    <cfRule type="duplicateValues" dxfId="19" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C127:C129">
-    <cfRule type="cellIs" dxfId="16" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="38" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C129">
-    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131">
-    <cfRule type="duplicateValues" dxfId="9" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:K132">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L125:S131">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP125:AU125">
-    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ128:AQ129">
-    <cfRule type="cellIs" dxfId="4" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ARQ/Ontologia_Arquitetura.xlsx
+++ b/Versão5/ARQ/Ontologia_Arquitetura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD47049-A42C-4354-BF85-8C2662EADDF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC55F2D-9AAD-4DAF-9DF8-3B1E559898D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13142" uniqueCount="2032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13497" uniqueCount="2033">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -6168,6 +6168,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -6785,43 +6788,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="52">
     <dxf>
       <font>
         <b val="0"/>
@@ -7197,6 +7164,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -7932,7 +7909,7 @@
       </c>
       <c r="B18" s="28">
         <f ca="1">NOW()</f>
-        <v>46268.512242708333</v>
+        <v>46268.689959143521</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>1328</v>
@@ -8037,7 +8014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A56445-53D9-475A-B2C6-D376FC6516D5}">
-  <dimension ref="A1:AC355"/>
+  <dimension ref="A1:AD355"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="26" bestFit="1" customWidth="1"/>
@@ -8067,10 +8044,11 @@
     <col min="27" max="27" width="25.7109375" style="26" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6.85546875" style="26" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9" style="26" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.28515625" style="26"/>
+    <col min="30" max="30" width="6.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.28515625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="78" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="78" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="77">
         <v>1</v>
       </c>
@@ -8158,8 +8136,11 @@
       <c r="AC1" s="79" t="s">
         <v>2007</v>
       </c>
+      <c r="AD1" s="35" t="s">
+        <v>2032</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -8255,8 +8236,11 @@
       <c r="AC2" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD2" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -8352,8 +8336,11 @@
       <c r="AC3" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD3" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -8449,8 +8436,11 @@
       <c r="AC4" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD4" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
         <v>5</v>
       </c>
@@ -8546,8 +8536,11 @@
       <c r="AC5" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD5" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>6</v>
       </c>
@@ -8643,8 +8636,11 @@
       <c r="AC6" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD6" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>7</v>
       </c>
@@ -8740,8 +8736,11 @@
       <c r="AC7" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD7" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>8</v>
       </c>
@@ -8837,8 +8836,11 @@
       <c r="AC8" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD8" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>9</v>
       </c>
@@ -8934,8 +8936,11 @@
       <c r="AC9" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD9" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -9031,8 +9036,11 @@
       <c r="AC10" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD10" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>11</v>
       </c>
@@ -9128,8 +9136,11 @@
       <c r="AC11" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD11" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>12</v>
       </c>
@@ -9225,8 +9236,11 @@
       <c r="AC12" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD12" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>13</v>
       </c>
@@ -9322,8 +9336,11 @@
       <c r="AC13" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD13" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21">
         <v>14</v>
       </c>
@@ -9419,8 +9436,11 @@
       <c r="AC14" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD14" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21">
         <v>15</v>
       </c>
@@ -9516,8 +9536,11 @@
       <c r="AC15" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD15" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>16</v>
       </c>
@@ -9613,8 +9636,11 @@
       <c r="AC16" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD16" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="21">
         <v>17</v>
       </c>
@@ -9710,8 +9736,11 @@
       <c r="AC17" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD17" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="21">
         <v>18</v>
       </c>
@@ -9807,8 +9836,11 @@
       <c r="AC18" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD18" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21">
         <v>19</v>
       </c>
@@ -9904,8 +9936,11 @@
       <c r="AC19" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD19" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="21">
         <v>20</v>
       </c>
@@ -10001,8 +10036,11 @@
       <c r="AC20" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD20" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="21">
         <v>21</v>
       </c>
@@ -10098,8 +10136,11 @@
       <c r="AC21" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD21" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21">
         <v>22</v>
       </c>
@@ -10195,8 +10236,11 @@
       <c r="AC22" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD22" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21">
         <v>23</v>
       </c>
@@ -10292,8 +10336,11 @@
       <c r="AC23" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD23" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="21">
         <v>24</v>
       </c>
@@ -10389,8 +10436,11 @@
       <c r="AC24" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD24" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="21">
         <v>25</v>
       </c>
@@ -10486,8 +10536,11 @@
       <c r="AC25" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD25" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21">
         <v>26</v>
       </c>
@@ -10583,8 +10636,11 @@
       <c r="AC26" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD26" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21">
         <v>27</v>
       </c>
@@ -10680,8 +10736,11 @@
       <c r="AC27" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD27" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21">
         <v>28</v>
       </c>
@@ -10777,8 +10836,11 @@
       <c r="AC28" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD28" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21">
         <v>29</v>
       </c>
@@ -10874,8 +10936,11 @@
       <c r="AC29" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD29" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21">
         <v>30</v>
       </c>
@@ -10971,8 +11036,11 @@
       <c r="AC30" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD30" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21">
         <v>31</v>
       </c>
@@ -11068,8 +11136,11 @@
       <c r="AC31" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD31" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="21">
         <v>32</v>
       </c>
@@ -11165,8 +11236,11 @@
       <c r="AC32" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD32" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="21">
         <v>33</v>
       </c>
@@ -11262,8 +11336,11 @@
       <c r="AC33" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD33" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="21">
         <v>34</v>
       </c>
@@ -11359,8 +11436,11 @@
       <c r="AC34" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD34" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21">
         <v>35</v>
       </c>
@@ -11456,8 +11536,11 @@
       <c r="AC35" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD35" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="21">
         <v>36</v>
       </c>
@@ -11553,8 +11636,11 @@
       <c r="AC36" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD36" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="21">
         <v>37</v>
       </c>
@@ -11650,8 +11736,11 @@
       <c r="AC37" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD37" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="21">
         <v>38</v>
       </c>
@@ -11747,8 +11836,11 @@
       <c r="AC38" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD38" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="21">
         <v>39</v>
       </c>
@@ -11844,8 +11936,11 @@
       <c r="AC39" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD39" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="21">
         <v>40</v>
       </c>
@@ -11941,8 +12036,11 @@
       <c r="AC40" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD40" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="21">
         <v>41</v>
       </c>
@@ -12038,8 +12136,11 @@
       <c r="AC41" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD41" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="21">
         <v>42</v>
       </c>
@@ -12135,8 +12236,11 @@
       <c r="AC42" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD42" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="21">
         <v>43</v>
       </c>
@@ -12232,8 +12336,11 @@
       <c r="AC43" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD43" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="21">
         <v>44</v>
       </c>
@@ -12329,8 +12436,11 @@
       <c r="AC44" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD44" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21">
         <v>45</v>
       </c>
@@ -12426,8 +12536,11 @@
       <c r="AC45" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD45" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21">
         <v>46</v>
       </c>
@@ -12523,8 +12636,11 @@
       <c r="AC46" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD46" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21">
         <v>47</v>
       </c>
@@ -12620,8 +12736,11 @@
       <c r="AC47" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD47" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21">
         <v>48</v>
       </c>
@@ -12717,8 +12836,11 @@
       <c r="AC48" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD48" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21">
         <v>49</v>
       </c>
@@ -12814,8 +12936,11 @@
       <c r="AC49" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD49" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21">
         <v>50</v>
       </c>
@@ -12911,8 +13036,11 @@
       <c r="AC50" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD50" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21">
         <v>51</v>
       </c>
@@ -13008,8 +13136,11 @@
       <c r="AC51" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD51" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="21">
         <v>52</v>
       </c>
@@ -13105,8 +13236,11 @@
       <c r="AC52" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD52" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21">
         <v>53</v>
       </c>
@@ -13202,8 +13336,11 @@
       <c r="AC53" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD53" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21">
         <v>54</v>
       </c>
@@ -13299,8 +13436,11 @@
       <c r="AC54" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD54" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21">
         <v>55</v>
       </c>
@@ -13396,8 +13536,11 @@
       <c r="AC55" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD55" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21">
         <v>56</v>
       </c>
@@ -13493,8 +13636,11 @@
       <c r="AC56" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD56" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21">
         <v>57</v>
       </c>
@@ -13590,8 +13736,11 @@
       <c r="AC57" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD57" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21">
         <v>58</v>
       </c>
@@ -13687,8 +13836,11 @@
       <c r="AC58" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD58" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21">
         <v>59</v>
       </c>
@@ -13784,8 +13936,11 @@
       <c r="AC59" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD59" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21">
         <v>60</v>
       </c>
@@ -13881,8 +14036,11 @@
       <c r="AC60" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD60" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21">
         <v>61</v>
       </c>
@@ -13978,8 +14136,11 @@
       <c r="AC61" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD61" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21">
         <v>62</v>
       </c>
@@ -14075,8 +14236,11 @@
       <c r="AC62" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD62" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21">
         <v>63</v>
       </c>
@@ -14172,8 +14336,11 @@
       <c r="AC63" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD63" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21">
         <v>64</v>
       </c>
@@ -14269,8 +14436,11 @@
       <c r="AC64" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD64" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21">
         <v>65</v>
       </c>
@@ -14366,8 +14536,11 @@
       <c r="AC65" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD65" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21">
         <v>66</v>
       </c>
@@ -14463,8 +14636,11 @@
       <c r="AC66" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD66" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21">
         <v>67</v>
       </c>
@@ -14560,8 +14736,11 @@
       <c r="AC67" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD67" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="21">
         <v>68</v>
       </c>
@@ -14657,8 +14836,11 @@
       <c r="AC68" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD68" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21">
         <v>69</v>
       </c>
@@ -14754,8 +14936,11 @@
       <c r="AC69" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD69" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="21">
         <v>70</v>
       </c>
@@ -14851,8 +15036,11 @@
       <c r="AC70" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD70" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="21">
         <v>71</v>
       </c>
@@ -14948,8 +15136,11 @@
       <c r="AC71" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD71" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="21">
         <v>72</v>
       </c>
@@ -15045,8 +15236,11 @@
       <c r="AC72" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD72" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="21">
         <v>73</v>
       </c>
@@ -15142,8 +15336,11 @@
       <c r="AC73" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD73" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="21">
         <v>74</v>
       </c>
@@ -15239,8 +15436,11 @@
       <c r="AC74" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD74" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="21">
         <v>75</v>
       </c>
@@ -15336,8 +15536,11 @@
       <c r="AC75" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD75" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="21">
         <v>76</v>
       </c>
@@ -15433,8 +15636,11 @@
       <c r="AC76" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD76" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="21">
         <v>77</v>
       </c>
@@ -15530,8 +15736,11 @@
       <c r="AC77" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD77" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="21">
         <v>78</v>
       </c>
@@ -15627,8 +15836,11 @@
       <c r="AC78" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD78" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="21">
         <v>79</v>
       </c>
@@ -15724,8 +15936,11 @@
       <c r="AC79" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD79" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="21">
         <v>80</v>
       </c>
@@ -15821,8 +16036,11 @@
       <c r="AC80" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD80" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="21">
         <v>81</v>
       </c>
@@ -15918,8 +16136,11 @@
       <c r="AC81" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD81" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="21">
         <v>82</v>
       </c>
@@ -16015,8 +16236,11 @@
       <c r="AC82" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD82" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="21">
         <v>83</v>
       </c>
@@ -16112,8 +16336,11 @@
       <c r="AC83" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD83" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="21">
         <v>84</v>
       </c>
@@ -16209,8 +16436,11 @@
       <c r="AC84" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD84" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="21">
         <v>85</v>
       </c>
@@ -16306,8 +16536,11 @@
       <c r="AC85" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD85" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="21">
         <v>86</v>
       </c>
@@ -16403,8 +16636,11 @@
       <c r="AC86" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD86" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="21">
         <v>87</v>
       </c>
@@ -16500,8 +16736,11 @@
       <c r="AC87" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD87" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="21">
         <v>88</v>
       </c>
@@ -16597,8 +16836,11 @@
       <c r="AC88" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD88" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="21">
         <v>89</v>
       </c>
@@ -16694,8 +16936,11 @@
       <c r="AC89" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD89" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="21">
         <v>90</v>
       </c>
@@ -16791,8 +17036,11 @@
       <c r="AC90" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD90" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="21">
         <v>91</v>
       </c>
@@ -16888,8 +17136,11 @@
       <c r="AC91" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD91" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="21">
         <v>92</v>
       </c>
@@ -16985,8 +17236,11 @@
       <c r="AC92" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD92" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="21">
         <v>93</v>
       </c>
@@ -17082,8 +17336,11 @@
       <c r="AC93" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD93" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="21">
         <v>94</v>
       </c>
@@ -17179,8 +17436,11 @@
       <c r="AC94" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD94" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="21">
         <v>95</v>
       </c>
@@ -17276,8 +17536,11 @@
       <c r="AC95" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD95" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="21">
         <v>96</v>
       </c>
@@ -17373,8 +17636,11 @@
       <c r="AC96" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD96" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="21">
         <v>97</v>
       </c>
@@ -17470,8 +17736,11 @@
       <c r="AC97" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD97" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="98" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="21">
         <v>98</v>
       </c>
@@ -17567,8 +17836,11 @@
       <c r="AC98" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD98" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="99" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="21">
         <v>99</v>
       </c>
@@ -17664,8 +17936,11 @@
       <c r="AC99" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD99" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="100" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="21">
         <v>100</v>
       </c>
@@ -17761,8 +18036,11 @@
       <c r="AC100" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD100" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="101" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="21">
         <v>101</v>
       </c>
@@ -17858,8 +18136,11 @@
       <c r="AC101" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD101" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="102" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="21">
         <v>102</v>
       </c>
@@ -17955,8 +18236,11 @@
       <c r="AC102" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD102" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="103" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="21">
         <v>103</v>
       </c>
@@ -18052,8 +18336,11 @@
       <c r="AC103" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD103" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="104" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="21">
         <v>104</v>
       </c>
@@ -18149,8 +18436,11 @@
       <c r="AC104" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD104" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="105" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="21">
         <v>105</v>
       </c>
@@ -18246,8 +18536,11 @@
       <c r="AC105" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD105" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="106" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="21">
         <v>106</v>
       </c>
@@ -18343,8 +18636,11 @@
       <c r="AC106" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD106" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="107" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="21">
         <v>107</v>
       </c>
@@ -18440,8 +18736,11 @@
       <c r="AC107" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD107" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="108" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="21">
         <v>108</v>
       </c>
@@ -18537,8 +18836,11 @@
       <c r="AC108" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD108" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="109" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="21">
         <v>109</v>
       </c>
@@ -18634,8 +18936,11 @@
       <c r="AC109" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD109" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="110" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="21">
         <v>110</v>
       </c>
@@ -18731,8 +19036,11 @@
       <c r="AC110" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD110" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="111" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="21">
         <v>111</v>
       </c>
@@ -18828,8 +19136,11 @@
       <c r="AC111" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD111" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="112" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="21">
         <v>112</v>
       </c>
@@ -18925,8 +19236,11 @@
       <c r="AC112" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD112" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="113" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="21">
         <v>113</v>
       </c>
@@ -19022,8 +19336,11 @@
       <c r="AC113" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD113" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="114" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="21">
         <v>114</v>
       </c>
@@ -19119,8 +19436,11 @@
       <c r="AC114" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD114" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="115" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="21">
         <v>115</v>
       </c>
@@ -19216,8 +19536,11 @@
       <c r="AC115" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD115" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="116" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="21">
         <v>116</v>
       </c>
@@ -19313,8 +19636,11 @@
       <c r="AC116" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD116" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="117" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="21">
         <v>117</v>
       </c>
@@ -19410,8 +19736,11 @@
       <c r="AC117" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD117" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="118" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="21">
         <v>118</v>
       </c>
@@ -19507,8 +19836,11 @@
       <c r="AC118" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD118" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="119" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="21">
         <v>119</v>
       </c>
@@ -19604,8 +19936,11 @@
       <c r="AC119" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD119" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="120" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="21">
         <v>120</v>
       </c>
@@ -19701,8 +20036,11 @@
       <c r="AC120" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD120" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="121" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="21">
         <v>121</v>
       </c>
@@ -19798,8 +20136,11 @@
       <c r="AC121" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD121" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="122" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="21">
         <v>122</v>
       </c>
@@ -19895,8 +20236,11 @@
       <c r="AC122" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD122" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="123" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="21">
         <v>123</v>
       </c>
@@ -19992,8 +20336,11 @@
       <c r="AC123" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD123" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="124" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="21">
         <v>124</v>
       </c>
@@ -20089,8 +20436,11 @@
       <c r="AC124" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD124" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="125" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="21">
         <v>125</v>
       </c>
@@ -20186,8 +20536,11 @@
       <c r="AC125" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD125" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="126" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="21">
         <v>126</v>
       </c>
@@ -20283,8 +20636,11 @@
       <c r="AC126" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD126" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="127" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="21">
         <v>127</v>
       </c>
@@ -20380,8 +20736,11 @@
       <c r="AC127" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD127" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="128" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="21">
         <v>128</v>
       </c>
@@ -20477,8 +20836,11 @@
       <c r="AC128" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD128" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="129" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="21">
         <v>129</v>
       </c>
@@ -20574,8 +20936,11 @@
       <c r="AC129" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD129" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="130" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="21">
         <v>130</v>
       </c>
@@ -20671,8 +21036,11 @@
       <c r="AC130" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD130" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="131" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="21">
         <v>131</v>
       </c>
@@ -20768,8 +21136,11 @@
       <c r="AC131" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD131" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="132" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="21">
         <v>132</v>
       </c>
@@ -20865,8 +21236,11 @@
       <c r="AC132" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD132" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="133" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="21">
         <v>133</v>
       </c>
@@ -20962,8 +21336,11 @@
       <c r="AC133" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD133" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="134" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="21">
         <v>134</v>
       </c>
@@ -21059,8 +21436,11 @@
       <c r="AC134" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD134" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="135" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="21">
         <v>135</v>
       </c>
@@ -21156,8 +21536,11 @@
       <c r="AC135" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD135" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="136" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="21">
         <v>136</v>
       </c>
@@ -21253,8 +21636,11 @@
       <c r="AC136" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD136" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="137" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="21">
         <v>137</v>
       </c>
@@ -21350,8 +21736,11 @@
       <c r="AC137" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD137" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="138" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="21">
         <v>138</v>
       </c>
@@ -21447,8 +21836,11 @@
       <c r="AC138" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD138" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="139" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="21">
         <v>139</v>
       </c>
@@ -21544,8 +21936,11 @@
       <c r="AC139" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD139" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="140" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="21">
         <v>140</v>
       </c>
@@ -21641,8 +22036,11 @@
       <c r="AC140" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD140" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="141" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="21">
         <v>141</v>
       </c>
@@ -21738,8 +22136,11 @@
       <c r="AC141" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD141" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="142" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="21">
         <v>142</v>
       </c>
@@ -21835,8 +22236,11 @@
       <c r="AC142" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD142" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="143" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="21">
         <v>143</v>
       </c>
@@ -21932,8 +22336,11 @@
       <c r="AC143" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD143" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="144" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="21">
         <v>144</v>
       </c>
@@ -22029,8 +22436,11 @@
       <c r="AC144" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD144" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="145" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="21">
         <v>145</v>
       </c>
@@ -22126,8 +22536,11 @@
       <c r="AC145" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD145" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="146" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="21">
         <v>146</v>
       </c>
@@ -22223,8 +22636,11 @@
       <c r="AC146" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD146" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="147" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="21">
         <v>147</v>
       </c>
@@ -22320,8 +22736,11 @@
       <c r="AC147" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD147" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="148" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="21">
         <v>148</v>
       </c>
@@ -22417,8 +22836,11 @@
       <c r="AC148" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD148" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="149" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="21">
         <v>149</v>
       </c>
@@ -22514,8 +22936,11 @@
       <c r="AC149" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD149" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="150" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="21">
         <v>150</v>
       </c>
@@ -22611,8 +23036,11 @@
       <c r="AC150" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD150" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="151" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="21">
         <v>151</v>
       </c>
@@ -22708,8 +23136,11 @@
       <c r="AC151" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD151" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="152" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="21">
         <v>152</v>
       </c>
@@ -22805,8 +23236,11 @@
       <c r="AC152" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD152" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="153" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="21">
         <v>153</v>
       </c>
@@ -22902,8 +23336,11 @@
       <c r="AC153" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD153" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="154" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="21">
         <v>154</v>
       </c>
@@ -22999,8 +23436,11 @@
       <c r="AC154" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD154" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="155" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="21">
         <v>155</v>
       </c>
@@ -23096,8 +23536,11 @@
       <c r="AC155" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD155" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="156" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="21">
         <v>156</v>
       </c>
@@ -23193,8 +23636,11 @@
       <c r="AC156" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD156" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="157" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="21">
         <v>157</v>
       </c>
@@ -23290,8 +23736,11 @@
       <c r="AC157" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD157" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="158" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="21">
         <v>158</v>
       </c>
@@ -23387,8 +23836,11 @@
       <c r="AC158" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD158" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="159" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="21">
         <v>159</v>
       </c>
@@ -23484,8 +23936,11 @@
       <c r="AC159" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD159" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="160" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="21">
         <v>160</v>
       </c>
@@ -23581,8 +24036,11 @@
       <c r="AC160" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD160" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="161" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="21">
         <v>161</v>
       </c>
@@ -23678,8 +24136,11 @@
       <c r="AC161" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD161" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="162" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="21">
         <v>162</v>
       </c>
@@ -23775,8 +24236,11 @@
       <c r="AC162" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD162" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="163" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="21">
         <v>163</v>
       </c>
@@ -23872,8 +24336,11 @@
       <c r="AC163" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD163" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="164" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="21">
         <v>164</v>
       </c>
@@ -23969,8 +24436,11 @@
       <c r="AC164" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD164" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="165" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="21">
         <v>165</v>
       </c>
@@ -24066,8 +24536,11 @@
       <c r="AC165" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD165" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="166" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="21">
         <v>166</v>
       </c>
@@ -24163,8 +24636,11 @@
       <c r="AC166" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD166" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="167" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="21">
         <v>167</v>
       </c>
@@ -24260,8 +24736,11 @@
       <c r="AC167" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD167" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="168" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="21">
         <v>168</v>
       </c>
@@ -24357,8 +24836,11 @@
       <c r="AC168" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD168" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="169" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="21">
         <v>169</v>
       </c>
@@ -24454,8 +24936,11 @@
       <c r="AC169" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD169" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="170" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="21">
         <v>170</v>
       </c>
@@ -24551,8 +25036,11 @@
       <c r="AC170" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD170" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="171" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="21">
         <v>171</v>
       </c>
@@ -24648,8 +25136,11 @@
       <c r="AC171" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD171" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="172" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="21">
         <v>172</v>
       </c>
@@ -24745,8 +25236,11 @@
       <c r="AC172" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD172" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="173" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="21">
         <v>173</v>
       </c>
@@ -24842,8 +25336,11 @@
       <c r="AC173" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD173" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="174" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="21">
         <v>174</v>
       </c>
@@ -24939,8 +25436,11 @@
       <c r="AC174" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD174" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="175" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="21">
         <v>175</v>
       </c>
@@ -25036,8 +25536,11 @@
       <c r="AC175" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD175" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="176" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="21">
         <v>176</v>
       </c>
@@ -25133,8 +25636,11 @@
       <c r="AC176" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD176" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="177" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="21">
         <v>177</v>
       </c>
@@ -25230,8 +25736,11 @@
       <c r="AC177" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD177" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="178" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="21">
         <v>178</v>
       </c>
@@ -25327,8 +25836,11 @@
       <c r="AC178" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD178" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="179" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="21">
         <v>179</v>
       </c>
@@ -25424,8 +25936,11 @@
       <c r="AC179" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD179" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="180" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="21">
         <v>180</v>
       </c>
@@ -25521,8 +26036,11 @@
       <c r="AC180" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD180" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="181" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="21">
         <v>181</v>
       </c>
@@ -25618,8 +26136,11 @@
       <c r="AC181" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD181" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="182" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="21">
         <v>182</v>
       </c>
@@ -25715,8 +26236,11 @@
       <c r="AC182" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD182" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="183" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="21">
         <v>183</v>
       </c>
@@ -25812,8 +26336,11 @@
       <c r="AC183" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD183" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="184" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="21">
         <v>184</v>
       </c>
@@ -25909,8 +26436,11 @@
       <c r="AC184" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD184" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="185" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="21">
         <v>185</v>
       </c>
@@ -26006,8 +26536,11 @@
       <c r="AC185" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD185" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="186" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="21">
         <v>186</v>
       </c>
@@ -26103,8 +26636,11 @@
       <c r="AC186" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD186" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="187" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="21">
         <v>187</v>
       </c>
@@ -26200,8 +26736,11 @@
       <c r="AC187" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD187" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="188" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="21">
         <v>188</v>
       </c>
@@ -26297,8 +26836,11 @@
       <c r="AC188" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD188" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="189" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="21">
         <v>189</v>
       </c>
@@ -26394,8 +26936,11 @@
       <c r="AC189" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD189" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="190" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="21">
         <v>190</v>
       </c>
@@ -26491,8 +27036,11 @@
       <c r="AC190" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD190" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="191" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="21">
         <v>191</v>
       </c>
@@ -26588,8 +27136,11 @@
       <c r="AC191" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD191" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="192" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="21">
         <v>192</v>
       </c>
@@ -26685,8 +27236,11 @@
       <c r="AC192" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD192" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="193" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="21">
         <v>193</v>
       </c>
@@ -26782,8 +27336,11 @@
       <c r="AC193" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD193" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="194" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="21">
         <v>194</v>
       </c>
@@ -26879,8 +27436,11 @@
       <c r="AC194" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD194" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="195" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="21">
         <v>195</v>
       </c>
@@ -26976,8 +27536,11 @@
       <c r="AC195" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD195" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="196" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="21">
         <v>196</v>
       </c>
@@ -27073,8 +27636,11 @@
       <c r="AC196" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD196" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="197" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="21">
         <v>197</v>
       </c>
@@ -27170,8 +27736,11 @@
       <c r="AC197" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD197" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="198" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="21">
         <v>198</v>
       </c>
@@ -27267,8 +27836,11 @@
       <c r="AC198" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD198" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="199" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="21">
         <v>199</v>
       </c>
@@ -27364,8 +27936,11 @@
       <c r="AC199" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD199" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="200" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="21">
         <v>200</v>
       </c>
@@ -27461,8 +28036,11 @@
       <c r="AC200" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD200" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="201" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="21">
         <v>201</v>
       </c>
@@ -27558,8 +28136,11 @@
       <c r="AC201" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD201" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="202" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="21">
         <v>202</v>
       </c>
@@ -27655,8 +28236,11 @@
       <c r="AC202" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD202" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="203" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="21">
         <v>203</v>
       </c>
@@ -27752,8 +28336,11 @@
       <c r="AC203" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD203" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="204" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="21">
         <v>204</v>
       </c>
@@ -27849,8 +28436,11 @@
       <c r="AC204" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD204" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="205" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="21">
         <v>205</v>
       </c>
@@ -27946,8 +28536,11 @@
       <c r="AC205" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD205" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="206" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="21">
         <v>206</v>
       </c>
@@ -28043,8 +28636,11 @@
       <c r="AC206" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD206" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="207" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="21">
         <v>207</v>
       </c>
@@ -28140,8 +28736,11 @@
       <c r="AC207" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD207" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="208" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="21">
         <v>208</v>
       </c>
@@ -28237,8 +28836,11 @@
       <c r="AC208" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD208" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="209" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="21">
         <v>209</v>
       </c>
@@ -28334,8 +28936,11 @@
       <c r="AC209" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD209" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="210" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="21">
         <v>210</v>
       </c>
@@ -28431,8 +29036,11 @@
       <c r="AC210" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD210" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="211" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="21">
         <v>211</v>
       </c>
@@ -28528,8 +29136,11 @@
       <c r="AC211" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD211" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="212" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="21">
         <v>212</v>
       </c>
@@ -28625,8 +29236,11 @@
       <c r="AC212" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD212" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="213" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="21">
         <v>213</v>
       </c>
@@ -28722,8 +29336,11 @@
       <c r="AC213" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD213" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="214" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="21">
         <v>214</v>
       </c>
@@ -28819,8 +29436,11 @@
       <c r="AC214" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD214" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="215" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="21">
         <v>215</v>
       </c>
@@ -28916,8 +29536,11 @@
       <c r="AC215" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD215" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="216" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="21">
         <v>216</v>
       </c>
@@ -29013,8 +29636,11 @@
       <c r="AC216" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD216" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="217" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="21">
         <v>217</v>
       </c>
@@ -29110,8 +29736,11 @@
       <c r="AC217" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD217" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="218" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="21">
         <v>218</v>
       </c>
@@ -29207,8 +29836,11 @@
       <c r="AC218" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD218" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="219" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="21">
         <v>219</v>
       </c>
@@ -29304,8 +29936,11 @@
       <c r="AC219" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD219" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="220" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="21">
         <v>220</v>
       </c>
@@ -29401,8 +30036,11 @@
       <c r="AC220" s="25" t="s">
         <v>1612</v>
       </c>
+      <c r="AD220" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="221" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="21">
         <v>221</v>
       </c>
@@ -29498,8 +30136,11 @@
       <c r="AC221" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD221" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="222" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="21">
         <v>222</v>
       </c>
@@ -29595,8 +30236,11 @@
       <c r="AC222" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD222" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="223" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="21">
         <v>223</v>
       </c>
@@ -29692,8 +30336,11 @@
       <c r="AC223" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD223" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="224" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="21">
         <v>224</v>
       </c>
@@ -29789,8 +30436,11 @@
       <c r="AC224" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD224" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="225" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="21">
         <v>225</v>
       </c>
@@ -29886,8 +30536,11 @@
       <c r="AC225" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD225" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="226" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="21">
         <v>226</v>
       </c>
@@ -29983,8 +30636,11 @@
       <c r="AC226" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD226" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="227" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="21">
         <v>227</v>
       </c>
@@ -30080,8 +30736,11 @@
       <c r="AC227" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD227" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="228" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="21">
         <v>228</v>
       </c>
@@ -30177,8 +30836,11 @@
       <c r="AC228" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD228" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="229" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="21">
         <v>229</v>
       </c>
@@ -30274,8 +30936,11 @@
       <c r="AC229" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD229" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="230" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="21">
         <v>230</v>
       </c>
@@ -30371,8 +31036,11 @@
       <c r="AC230" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD230" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="231" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="21">
         <v>231</v>
       </c>
@@ -30468,8 +31136,11 @@
       <c r="AC231" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD231" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="232" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="21">
         <v>232</v>
       </c>
@@ -30565,8 +31236,11 @@
       <c r="AC232" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD232" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="233" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="21">
         <v>233</v>
       </c>
@@ -30662,8 +31336,11 @@
       <c r="AC233" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD233" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="234" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="21">
         <v>234</v>
       </c>
@@ -30759,8 +31436,11 @@
       <c r="AC234" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD234" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="235" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="21">
         <v>235</v>
       </c>
@@ -30856,8 +31536,11 @@
       <c r="AC235" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD235" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="236" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="21">
         <v>236</v>
       </c>
@@ -30953,8 +31636,11 @@
       <c r="AC236" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD236" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="237" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="21">
         <v>237</v>
       </c>
@@ -31050,8 +31736,11 @@
       <c r="AC237" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD237" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="238" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="21">
         <v>238</v>
       </c>
@@ -31147,8 +31836,11 @@
       <c r="AC238" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD238" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="239" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="21">
         <v>239</v>
       </c>
@@ -31244,8 +31936,11 @@
       <c r="AC239" s="25" t="s">
         <v>1604</v>
       </c>
+      <c r="AD239" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="240" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="21">
         <v>240</v>
       </c>
@@ -31341,8 +32036,11 @@
       <c r="AC240" s="25" t="s">
         <v>1604</v>
       </c>
+      <c r="AD240" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="241" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="21">
         <v>241</v>
       </c>
@@ -31438,8 +32136,11 @@
       <c r="AC241" s="25" t="s">
         <v>1604</v>
       </c>
+      <c r="AD241" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="242" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="21">
         <v>242</v>
       </c>
@@ -31535,8 +32236,11 @@
       <c r="AC242" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD242" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="243" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="21">
         <v>243</v>
       </c>
@@ -31632,8 +32336,11 @@
       <c r="AC243" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD243" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="244" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="21">
         <v>244</v>
       </c>
@@ -31729,8 +32436,11 @@
       <c r="AC244" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD244" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="245" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="21">
         <v>245</v>
       </c>
@@ -31826,8 +32536,11 @@
       <c r="AC245" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD245" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="246" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="21">
         <v>246</v>
       </c>
@@ -31923,8 +32636,11 @@
       <c r="AC246" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD246" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="247" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="21">
         <v>247</v>
       </c>
@@ -32020,8 +32736,11 @@
       <c r="AC247" s="25" t="s">
         <v>1603</v>
       </c>
+      <c r="AD247" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="248" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="21">
         <v>248</v>
       </c>
@@ -32117,8 +32836,11 @@
       <c r="AC248" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD248" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="249" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="21">
         <v>249</v>
       </c>
@@ -32214,8 +32936,11 @@
       <c r="AC249" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD249" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="250" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="21">
         <v>250</v>
       </c>
@@ -32311,8 +33036,11 @@
       <c r="AC250" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD250" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="251" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="21">
         <v>251</v>
       </c>
@@ -32408,8 +33136,11 @@
       <c r="AC251" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD251" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="252" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="21">
         <v>252</v>
       </c>
@@ -32505,8 +33236,11 @@
       <c r="AC252" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD252" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="253" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="21">
         <v>253</v>
       </c>
@@ -32602,8 +33336,11 @@
       <c r="AC253" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD253" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="254" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="21">
         <v>254</v>
       </c>
@@ -32699,8 +33436,11 @@
       <c r="AC254" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD254" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="255" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="21">
         <v>255</v>
       </c>
@@ -32796,8 +33536,11 @@
       <c r="AC255" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD255" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="256" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="21">
         <v>256</v>
       </c>
@@ -32893,8 +33636,11 @@
       <c r="AC256" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD256" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="257" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="21">
         <v>257</v>
       </c>
@@ -32990,8 +33736,11 @@
       <c r="AC257" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD257" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="258" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="21">
         <v>258</v>
       </c>
@@ -33087,8 +33836,11 @@
       <c r="AC258" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD258" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="259" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="21">
         <v>259</v>
       </c>
@@ -33184,8 +33936,11 @@
       <c r="AC259" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD259" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="260" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="21">
         <v>260</v>
       </c>
@@ -33281,8 +34036,11 @@
       <c r="AC260" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD260" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="261" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="21">
         <v>261</v>
       </c>
@@ -33378,8 +34136,11 @@
       <c r="AC261" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD261" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="262" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="21">
         <v>262</v>
       </c>
@@ -33475,8 +34236,11 @@
       <c r="AC262" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD262" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="263" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="21">
         <v>263</v>
       </c>
@@ -33572,8 +34336,11 @@
       <c r="AC263" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD263" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="264" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="21">
         <v>264</v>
       </c>
@@ -33669,8 +34436,11 @@
       <c r="AC264" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD264" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="265" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="21">
         <v>265</v>
       </c>
@@ -33766,8 +34536,11 @@
       <c r="AC265" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD265" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="266" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="21">
         <v>266</v>
       </c>
@@ -33863,8 +34636,11 @@
       <c r="AC266" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD266" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="267" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="21">
         <v>267</v>
       </c>
@@ -33960,8 +34736,11 @@
       <c r="AC267" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD267" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="268" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="21">
         <v>268</v>
       </c>
@@ -34057,8 +34836,11 @@
       <c r="AC268" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD268" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="269" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="21">
         <v>269</v>
       </c>
@@ -34154,8 +34936,11 @@
       <c r="AC269" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD269" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="270" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="21">
         <v>270</v>
       </c>
@@ -34251,8 +35036,11 @@
       <c r="AC270" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD270" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="271" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="21">
         <v>271</v>
       </c>
@@ -34348,8 +35136,11 @@
       <c r="AC271" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD271" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="272" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="21">
         <v>272</v>
       </c>
@@ -34445,8 +35236,11 @@
       <c r="AC272" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD272" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="273" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="21">
         <v>273</v>
       </c>
@@ -34542,8 +35336,11 @@
       <c r="AC273" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD273" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="274" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="21">
         <v>274</v>
       </c>
@@ -34639,8 +35436,11 @@
       <c r="AC274" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD274" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="275" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="21">
         <v>275</v>
       </c>
@@ -34736,8 +35536,11 @@
       <c r="AC275" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD275" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="276" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="21">
         <v>276</v>
       </c>
@@ -34833,8 +35636,11 @@
       <c r="AC276" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD276" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="277" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="21">
         <v>277</v>
       </c>
@@ -34930,8 +35736,11 @@
       <c r="AC277" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD277" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="278" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="21">
         <v>278</v>
       </c>
@@ -35027,8 +35836,11 @@
       <c r="AC278" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD278" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="279" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="21">
         <v>279</v>
       </c>
@@ -35124,8 +35936,11 @@
       <c r="AC279" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD279" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="280" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="21">
         <v>280</v>
       </c>
@@ -35221,8 +36036,11 @@
       <c r="AC280" s="25" t="s">
         <v>1601</v>
       </c>
+      <c r="AD280" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="281" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="21">
         <v>281</v>
       </c>
@@ -35318,8 +36136,11 @@
       <c r="AC281" s="25" t="s">
         <v>1336</v>
       </c>
+      <c r="AD281" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="282" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="21">
         <v>282</v>
       </c>
@@ -35415,8 +36236,11 @@
       <c r="AC282" s="25" t="s">
         <v>1336</v>
       </c>
+      <c r="AD282" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="283" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="21">
         <v>283</v>
       </c>
@@ -35512,8 +36336,11 @@
       <c r="AC283" s="25" t="s">
         <v>1336</v>
       </c>
+      <c r="AD283" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="284" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="21">
         <v>284</v>
       </c>
@@ -35609,8 +36436,11 @@
       <c r="AC284" s="25" t="s">
         <v>1336</v>
       </c>
+      <c r="AD284" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="285" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="21">
         <v>285</v>
       </c>
@@ -35706,8 +36536,11 @@
       <c r="AC285" s="25" t="s">
         <v>1336</v>
       </c>
+      <c r="AD285" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="286" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="21">
         <v>286</v>
       </c>
@@ -35803,8 +36636,11 @@
       <c r="AC286" s="25" t="s">
         <v>1336</v>
       </c>
+      <c r="AD286" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="287" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="21">
         <v>287</v>
       </c>
@@ -35900,8 +36736,11 @@
       <c r="AC287" s="25" t="s">
         <v>1336</v>
       </c>
+      <c r="AD287" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="288" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="21">
         <v>288</v>
       </c>
@@ -35997,8 +36836,11 @@
       <c r="AC288" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD288" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="289" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="21">
         <v>289</v>
       </c>
@@ -36094,8 +36936,11 @@
       <c r="AC289" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD289" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="290" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="21">
         <v>290</v>
       </c>
@@ -36191,8 +37036,11 @@
       <c r="AC290" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD290" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="291" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="21">
         <v>291</v>
       </c>
@@ -36288,8 +37136,11 @@
       <c r="AC291" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD291" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="292" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="21">
         <v>292</v>
       </c>
@@ -36385,8 +37236,11 @@
       <c r="AC292" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD292" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="293" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="21">
         <v>293</v>
       </c>
@@ -36482,8 +37336,11 @@
       <c r="AC293" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD293" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="294" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="21">
         <v>294</v>
       </c>
@@ -36579,8 +37436,11 @@
       <c r="AC294" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD294" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="295" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="21">
         <v>295</v>
       </c>
@@ -36676,8 +37536,11 @@
       <c r="AC295" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD295" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="296" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="21">
         <v>296</v>
       </c>
@@ -36773,8 +37636,11 @@
       <c r="AC296" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD296" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="297" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="21">
         <v>297</v>
       </c>
@@ -36870,8 +37736,11 @@
       <c r="AC297" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD297" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="298" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="21">
         <v>298</v>
       </c>
@@ -36967,8 +37836,11 @@
       <c r="AC298" s="25" t="s">
         <v>1608</v>
       </c>
+      <c r="AD298" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="299" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="21">
         <v>299</v>
       </c>
@@ -37064,8 +37936,11 @@
       <c r="AC299" s="25" t="s">
         <v>1609</v>
       </c>
+      <c r="AD299" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="300" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="21">
         <v>300</v>
       </c>
@@ -37161,8 +38036,11 @@
       <c r="AC300" s="25" t="s">
         <v>1609</v>
       </c>
+      <c r="AD300" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="301" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="21">
         <v>301</v>
       </c>
@@ -37258,8 +38136,11 @@
       <c r="AC301" s="25" t="s">
         <v>1609</v>
       </c>
+      <c r="AD301" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="302" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="21">
         <v>302</v>
       </c>
@@ -37355,8 +38236,11 @@
       <c r="AC302" s="25" t="s">
         <v>1609</v>
       </c>
+      <c r="AD302" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="303" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="21">
         <v>303</v>
       </c>
@@ -37452,8 +38336,11 @@
       <c r="AC303" s="25" t="s">
         <v>1609</v>
       </c>
+      <c r="AD303" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="304" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="21">
         <v>304</v>
       </c>
@@ -37549,8 +38436,11 @@
       <c r="AC304" s="25" t="s">
         <v>1609</v>
       </c>
+      <c r="AD304" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="305" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="21">
         <v>305</v>
       </c>
@@ -37646,8 +38536,11 @@
       <c r="AC305" s="25" t="s">
         <v>1613</v>
       </c>
+      <c r="AD305" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="306" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="21">
         <v>306</v>
       </c>
@@ -37743,8 +38636,11 @@
       <c r="AC306" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD306" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="307" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="21">
         <v>307</v>
       </c>
@@ -37840,8 +38736,11 @@
       <c r="AC307" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD307" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="308" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="21">
         <v>308</v>
       </c>
@@ -37937,8 +38836,11 @@
       <c r="AC308" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD308" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="309" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="21">
         <v>309</v>
       </c>
@@ -38034,8 +38936,11 @@
       <c r="AC309" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD309" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="310" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="21">
         <v>310</v>
       </c>
@@ -38131,8 +39036,11 @@
       <c r="AC310" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD310" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="311" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="21">
         <v>311</v>
       </c>
@@ -38228,8 +39136,11 @@
       <c r="AC311" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD311" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="312" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="21">
         <v>312</v>
       </c>
@@ -38325,8 +39236,11 @@
       <c r="AC312" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD312" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="313" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="21">
         <v>313</v>
       </c>
@@ -38422,8 +39336,11 @@
       <c r="AC313" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD313" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="314" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="21">
         <v>314</v>
       </c>
@@ -38519,8 +39436,11 @@
       <c r="AC314" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD314" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="315" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="21">
         <v>315</v>
       </c>
@@ -38616,8 +39536,11 @@
       <c r="AC315" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD315" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="316" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="21">
         <v>316</v>
       </c>
@@ -38713,8 +39636,11 @@
       <c r="AC316" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD316" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="317" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="21">
         <v>317</v>
       </c>
@@ -38811,8 +39737,11 @@
       <c r="AC317" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD317" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="318" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="21">
         <v>318</v>
       </c>
@@ -38909,8 +39838,11 @@
       <c r="AC318" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD318" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="319" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="21">
         <v>319</v>
       </c>
@@ -39007,8 +39939,11 @@
       <c r="AC319" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD319" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="320" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="21">
         <v>320</v>
       </c>
@@ -39087,7 +40022,7 @@
         <v>81</v>
       </c>
       <c r="X320" s="57" t="str">
-        <f t="shared" ref="X320:X351" si="80">CONCATENATE("Key-ARQ-",A320)</f>
+        <f t="shared" ref="X320:X350" si="80">CONCATENATE("Key-ARQ-",A320)</f>
         <v>Key-ARQ-320</v>
       </c>
       <c r="Y320" s="19" t="s">
@@ -39105,8 +40040,11 @@
       <c r="AC320" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD320" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="321" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="21">
         <v>321</v>
       </c>
@@ -39203,8 +40141,11 @@
       <c r="AC321" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD321" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="322" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="21">
         <v>322</v>
       </c>
@@ -39301,8 +40242,11 @@
       <c r="AC322" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD322" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="323" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="21">
         <v>323</v>
       </c>
@@ -39399,8 +40343,11 @@
       <c r="AC323" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD323" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="324" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="21">
         <v>324</v>
       </c>
@@ -39497,8 +40444,11 @@
       <c r="AC324" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD324" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="325" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="21">
         <v>325</v>
       </c>
@@ -39595,8 +40545,11 @@
       <c r="AC325" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD325" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="326" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="21">
         <v>326</v>
       </c>
@@ -39693,8 +40646,11 @@
       <c r="AC326" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD326" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="327" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="21">
         <v>327</v>
       </c>
@@ -39791,8 +40747,11 @@
       <c r="AC327" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD327" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="328" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="21">
         <v>328</v>
       </c>
@@ -39889,8 +40848,11 @@
       <c r="AC328" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD328" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="329" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="21">
         <v>329</v>
       </c>
@@ -39987,8 +40949,11 @@
       <c r="AC329" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD329" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="330" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="21">
         <v>330</v>
       </c>
@@ -40084,8 +41049,11 @@
       <c r="AC330" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD330" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="331" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="21">
         <v>331</v>
       </c>
@@ -40181,8 +41149,11 @@
       <c r="AC331" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD331" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="332" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="21">
         <v>332</v>
       </c>
@@ -40278,8 +41249,11 @@
       <c r="AC332" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD332" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="333" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="21">
         <v>333</v>
       </c>
@@ -40375,8 +41349,11 @@
       <c r="AC333" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD333" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="334" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="21">
         <v>334</v>
       </c>
@@ -40472,8 +41449,11 @@
       <c r="AC334" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD334" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="335" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="21">
         <v>335</v>
       </c>
@@ -40569,8 +41549,11 @@
       <c r="AC335" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD335" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="336" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="21">
         <v>336</v>
       </c>
@@ -40666,8 +41649,11 @@
       <c r="AC336" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD336" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="337" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="21">
         <v>337</v>
       </c>
@@ -40763,8 +41749,11 @@
       <c r="AC337" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD337" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="338" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="21">
         <v>338</v>
       </c>
@@ -40860,8 +41849,11 @@
       <c r="AC338" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD338" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="339" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="21">
         <v>339</v>
       </c>
@@ -40957,8 +41949,11 @@
       <c r="AC339" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD339" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="340" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="21">
         <v>340</v>
       </c>
@@ -41054,8 +42049,11 @@
       <c r="AC340" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD340" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="341" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="21">
         <v>341</v>
       </c>
@@ -41151,8 +42149,11 @@
       <c r="AC341" s="25" t="s">
         <v>1607</v>
       </c>
+      <c r="AD341" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="342" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="21">
         <v>342</v>
       </c>
@@ -41249,8 +42250,11 @@
       <c r="AC342" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="AD342" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="343" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="21">
         <v>343</v>
       </c>
@@ -41347,8 +42351,11 @@
       <c r="AC343" s="25" t="s">
         <v>1610</v>
       </c>
+      <c r="AD343" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="344" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="21">
         <v>344</v>
       </c>
@@ -41445,8 +42452,11 @@
       <c r="AC344" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD344" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="345" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="21">
         <v>345</v>
       </c>
@@ -41543,8 +42553,11 @@
       <c r="AC345" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD345" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="346" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="21">
         <v>346</v>
       </c>
@@ -41641,8 +42654,11 @@
       <c r="AC346" s="25" t="s">
         <v>1606</v>
       </c>
+      <c r="AD346" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="347" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="21">
         <v>347</v>
       </c>
@@ -41739,8 +42755,11 @@
       <c r="AC347" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD347" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="348" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="21">
         <v>348</v>
       </c>
@@ -41837,8 +42856,11 @@
       <c r="AC348" s="25" t="s">
         <v>1602</v>
       </c>
+      <c r="AD348" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="349" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="21">
         <v>349</v>
       </c>
@@ -41935,8 +42957,11 @@
       <c r="AC349" s="25" t="s">
         <v>1605</v>
       </c>
+      <c r="AD349" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="350" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="21">
         <v>350</v>
       </c>
@@ -42033,8 +43058,11 @@
       <c r="AC350" s="25" t="s">
         <v>1611</v>
       </c>
+      <c r="AD350" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="351" spans="1:29" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="21">
         <v>351</v>
       </c>
@@ -42093,7 +43121,7 @@
       <c r="R351" s="19" t="s">
         <v>2014</v>
       </c>
-      <c r="S351" s="19" t="s">
+      <c r="S351" s="43" t="s">
         <v>9</v>
       </c>
       <c r="T351" s="19" t="str">
@@ -42130,8 +43158,11 @@
       <c r="AC351" s="80" t="s">
         <v>9</v>
       </c>
+      <c r="AD351" s="25" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="352" spans="1:29" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="21">
         <v>352</v>
       </c>
@@ -42190,7 +43221,7 @@
       <c r="R352" s="19" t="s">
         <v>2018</v>
       </c>
-      <c r="S352" s="19" t="s">
+      <c r="S352" s="43" t="s">
         <v>9</v>
       </c>
       <c r="T352" s="19" t="str">
@@ -42227,8 +43258,11 @@
       <c r="AC352" s="80" t="s">
         <v>9</v>
       </c>
+      <c r="AD352" s="80" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="353" spans="1:29" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="21">
         <v>353</v>
       </c>
@@ -42287,7 +43321,7 @@
       <c r="R353" s="19" t="s">
         <v>2022</v>
       </c>
-      <c r="S353" s="19" t="s">
+      <c r="S353" s="43" t="s">
         <v>9</v>
       </c>
       <c r="T353" s="19" t="str">
@@ -42324,8 +43358,11 @@
       <c r="AC353" s="80" t="s">
         <v>9</v>
       </c>
+      <c r="AD353" s="80" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="354" spans="1:29" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="21">
         <v>354</v>
       </c>
@@ -42384,7 +43421,7 @@
       <c r="R354" s="19" t="s">
         <v>2026</v>
       </c>
-      <c r="S354" s="19" t="s">
+      <c r="S354" s="43" t="s">
         <v>9</v>
       </c>
       <c r="T354" s="19" t="str">
@@ -42421,8 +43458,11 @@
       <c r="AC354" s="80" t="s">
         <v>9</v>
       </c>
+      <c r="AD354" s="80" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="355" spans="1:29" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="21">
         <v>355</v>
       </c>
@@ -42481,7 +43521,7 @@
       <c r="R355" s="19" t="s">
         <v>2031</v>
       </c>
-      <c r="S355" s="19" t="s">
+      <c r="S355" s="43" t="s">
         <v>9</v>
       </c>
       <c r="T355" s="19" t="str">
@@ -42516,6 +43556,9 @@
         <v>9</v>
       </c>
       <c r="AC355" s="80" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD355" s="80" t="s">
         <v>9</v>
       </c>
     </row>
@@ -42524,53 +43567,53 @@
     <sortCondition ref="A1:A350"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A351:B355">
+    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E355:F355">
+    <cfRule type="duplicateValues" dxfId="50" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F350 F356:F1048576">
-    <cfRule type="duplicateValues" dxfId="53" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17:F36">
-    <cfRule type="duplicateValues" dxfId="52" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F270">
-    <cfRule type="duplicateValues" dxfId="51" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F271:F272 F274:F279 F1:F16 F281:F350 F37:F269 F356:F1048576">
-    <cfRule type="duplicateValues" dxfId="50" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F271:F272 F274:F279 F281:F350 F1:F269 F356:F1048576">
-    <cfRule type="duplicateValues" dxfId="49" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F273">
-    <cfRule type="duplicateValues" dxfId="48" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F280">
-    <cfRule type="duplicateValues" dxfId="47" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="543"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F351:F354">
+    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F356:F1048576">
-    <cfRule type="duplicateValues" dxfId="45" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="670"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:X1 AA1:AA342 A1:F350 L1:R350 AD1:XFD350 T2:W350 A356:F1048576 L356:X1048576 AD356:XFD1048576 A351:A355 W351:W355">
-    <cfRule type="cellIs" dxfId="0" priority="23" operator="equal">
+  <conditionalFormatting sqref="S1:X1 AA1:AA342 A1:F350 L1:R350 AE1:XFD350 T2:W350 W351:W355 A356:F1048576 L356:X1048576 AE356:XFD1048576">
+    <cfRule type="cellIs" dxfId="40" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X356:X1048576 X1">
-    <cfRule type="duplicateValues" dxfId="43" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA344:AA350 AA356:AA1048576">
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B351:B355">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E355:F355">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F351:F354">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -42719,7 +43762,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42791,15 +43834,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B2:G1048576">
-    <cfRule type="containsText" dxfId="40" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="38" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -62544,106 +63587,106 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1 B2:B31 B113:B132 A133:B1048576 D1:I1048576 L1:XFD124 A2:A132 T125:AO125 T126:XFD126 T127:AS127 AT127:XFD129 T128:AP129 AR128:AS129 T130:XFD131 L132:XFD1048576">
-    <cfRule type="cellIs" dxfId="37" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="88" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B31 B113:B1048576">
-    <cfRule type="duplicateValues" dxfId="36" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="35" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:B57">
-    <cfRule type="cellIs" dxfId="34" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="82" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B66">
-    <cfRule type="duplicateValues" dxfId="32" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B112">
-    <cfRule type="cellIs" dxfId="31" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="75" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67:B74">
-    <cfRule type="duplicateValues" dxfId="30" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75:B86">
-    <cfRule type="duplicateValues" dxfId="29" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75:B112">
-    <cfRule type="duplicateValues" dxfId="28" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="27" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130:B1048576 B113:B124">
-    <cfRule type="duplicateValues" dxfId="26" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C31">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C86">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C126">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C127">
-    <cfRule type="duplicateValues" dxfId="19" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C127:C129">
-    <cfRule type="cellIs" dxfId="16" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="38" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C129">
-    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131">
-    <cfRule type="duplicateValues" dxfId="9" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:K132">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L125:S131">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP125:AU125">
-    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ128:AQ129">
-    <cfRule type="cellIs" dxfId="4" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ARQ/Ontologia_Arquitetura.xlsx
+++ b/Versão5/ARQ/Ontologia_Arquitetura.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC55F2D-9AAD-4DAF-9DF8-3B1E559898D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457ABABB-17D4-48FE-BAA3-ED71B602F4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13497" uniqueCount="2033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13532" uniqueCount="2045">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -6098,15 +6098,6 @@
     <t>Código ABNT</t>
   </si>
   <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>Função.Auxiliar</t>
   </si>
   <si>
@@ -6155,9 +6146,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -6171,6 +6159,54 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -6763,9 +6799,6 @@
     <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6784,11 +6817,50 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="55">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -7156,14 +7228,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -7909,7 +7973,7 @@
       </c>
       <c r="B18" s="28">
         <f ca="1">NOW()</f>
-        <v>46268.689959143521</v>
+        <v>46273.518603703706</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>1328</v>
@@ -8033,7 +8097,7 @@
     <col min="16" max="16" width="139.140625" style="26" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="122.5703125" style="26" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="131.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.28515625" style="86" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="85" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.7109375" style="26" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15.28515625" style="26" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="13.28515625" style="26" bestFit="1" customWidth="1"/>
@@ -8067,19 +8131,19 @@
       <c r="F1" s="77" t="s">
         <v>1106</v>
       </c>
-      <c r="G1" s="82" t="s">
+      <c r="G1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="83" t="s">
+      <c r="H1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="83" t="s">
+      <c r="I1" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="82" t="s">
+      <c r="J1" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="82" t="s">
+      <c r="K1" s="81" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="44" t="s">
@@ -8103,7 +8167,7 @@
       <c r="R1" s="44" t="s">
         <v>1318</v>
       </c>
-      <c r="S1" s="85" t="s">
+      <c r="S1" s="84" t="s">
         <v>80</v>
       </c>
       <c r="T1" s="44" t="s">
@@ -8137,7 +8201,7 @@
         <v>2007</v>
       </c>
       <c r="AD1" s="35" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8162,10 +8226,10 @@
       <c r="G2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="84" t="s">
+      <c r="H2" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="7" t="s">
@@ -8262,10 +8326,10 @@
       <c r="G3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="84" t="s">
+      <c r="H3" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J3" s="7" t="s">
@@ -8362,10 +8426,10 @@
       <c r="G4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="84" t="s">
+      <c r="H4" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J4" s="7" t="s">
@@ -8462,10 +8526,10 @@
       <c r="G5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="84" t="s">
+      <c r="H5" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J5" s="7" t="s">
@@ -8562,10 +8626,10 @@
       <c r="G6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="84" t="s">
+      <c r="H6" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J6" s="7" t="s">
@@ -8662,10 +8726,10 @@
       <c r="G7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="84" t="s">
+      <c r="H7" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J7" s="7" t="s">
@@ -8762,10 +8826,10 @@
       <c r="G8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="84" t="s">
+      <c r="H8" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J8" s="7" t="s">
@@ -8862,10 +8926,10 @@
       <c r="G9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="84" t="s">
+      <c r="H9" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J9" s="7" t="s">
@@ -8962,10 +9026,10 @@
       <c r="G10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="84" t="s">
+      <c r="H10" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J10" s="7" t="s">
@@ -9062,10 +9126,10 @@
       <c r="G11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="84" t="s">
+      <c r="H11" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J11" s="7" t="s">
@@ -9162,10 +9226,10 @@
       <c r="G12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="84" t="s">
+      <c r="H12" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J12" s="7" t="s">
@@ -9262,10 +9326,10 @@
       <c r="G13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="84" t="s">
+      <c r="H13" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J13" s="7" t="s">
@@ -9362,10 +9426,10 @@
       <c r="G14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="84" t="s">
+      <c r="H14" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J14" s="7" t="s">
@@ -9462,10 +9526,10 @@
       <c r="G15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="84" t="s">
+      <c r="H15" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J15" s="7" t="s">
@@ -9562,10 +9626,10 @@
       <c r="G16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="84" t="s">
+      <c r="H16" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J16" s="7" t="s">
@@ -11662,10 +11726,10 @@
       <c r="G37" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H37" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="84" t="s">
+      <c r="H37" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J37" s="7" t="s">
@@ -11762,10 +11826,10 @@
       <c r="G38" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H38" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="84" t="s">
+      <c r="H38" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J38" s="7" t="s">
@@ -11862,10 +11926,10 @@
       <c r="G39" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H39" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="84" t="s">
+      <c r="H39" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J39" s="7" t="s">
@@ -11962,10 +12026,10 @@
       <c r="G40" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I40" s="84" t="s">
+      <c r="H40" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J40" s="7" t="s">
@@ -12062,10 +12126,10 @@
       <c r="G41" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" s="84" t="s">
+      <c r="H41" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -12162,10 +12226,10 @@
       <c r="G42" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H42" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I42" s="84" t="s">
+      <c r="H42" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J42" s="7" t="s">
@@ -12262,10 +12326,10 @@
       <c r="G43" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H43" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I43" s="84" t="s">
+      <c r="H43" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J43" s="7" t="s">
@@ -12362,10 +12426,10 @@
       <c r="G44" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H44" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I44" s="84" t="s">
+      <c r="H44" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J44" s="7" t="s">
@@ -12462,10 +12526,10 @@
       <c r="G45" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H45" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I45" s="84" t="s">
+      <c r="H45" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J45" s="7" t="s">
@@ -12562,10 +12626,10 @@
       <c r="G46" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H46" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I46" s="84" t="s">
+      <c r="H46" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I46" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J46" s="7" t="s">
@@ -12662,10 +12726,10 @@
       <c r="G47" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H47" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I47" s="84" t="s">
+      <c r="H47" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I47" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J47" s="7" t="s">
@@ -12762,10 +12826,10 @@
       <c r="G48" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H48" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I48" s="84" t="s">
+      <c r="H48" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I48" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J48" s="7" t="s">
@@ -12862,10 +12926,10 @@
       <c r="G49" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H49" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I49" s="84" t="s">
+      <c r="H49" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J49" s="7" t="s">
@@ -12962,10 +13026,10 @@
       <c r="G50" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H50" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I50" s="84" t="s">
+      <c r="H50" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I50" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J50" s="7" t="s">
@@ -13062,10 +13126,10 @@
       <c r="G51" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H51" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I51" s="84" t="s">
+      <c r="H51" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I51" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J51" s="7" t="s">
@@ -13162,10 +13226,10 @@
       <c r="G52" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H52" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I52" s="84" t="s">
+      <c r="H52" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I52" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J52" s="7" t="s">
@@ -13262,10 +13326,10 @@
       <c r="G53" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H53" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I53" s="84" t="s">
+      <c r="H53" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J53" s="7" t="s">
@@ -13362,10 +13426,10 @@
       <c r="G54" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I54" s="84" t="s">
+      <c r="H54" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J54" s="7" t="s">
@@ -13462,10 +13526,10 @@
       <c r="G55" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H55" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I55" s="84" t="s">
+      <c r="H55" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J55" s="7" t="s">
@@ -13562,10 +13626,10 @@
       <c r="G56" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H56" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I56" s="84" t="s">
+      <c r="H56" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J56" s="7" t="s">
@@ -13662,10 +13726,10 @@
       <c r="G57" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H57" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I57" s="84" t="s">
+      <c r="H57" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J57" s="7" t="s">
@@ -13762,10 +13826,10 @@
       <c r="G58" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H58" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I58" s="84" t="s">
+      <c r="H58" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J58" s="7" t="s">
@@ -13862,10 +13926,10 @@
       <c r="G59" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H59" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I59" s="84" t="s">
+      <c r="H59" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I59" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J59" s="7" t="s">
@@ -13962,10 +14026,10 @@
       <c r="G60" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H60" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I60" s="84" t="s">
+      <c r="H60" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I60" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J60" s="7" t="s">
@@ -14062,10 +14126,10 @@
       <c r="G61" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H61" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I61" s="84" t="s">
+      <c r="H61" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I61" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J61" s="7" t="s">
@@ -14162,10 +14226,10 @@
       <c r="G62" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H62" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I62" s="84" t="s">
+      <c r="H62" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I62" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J62" s="7" t="s">
@@ -14262,10 +14326,10 @@
       <c r="G63" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H63" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I63" s="84" t="s">
+      <c r="H63" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I63" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J63" s="7" t="s">
@@ -14362,10 +14426,10 @@
       <c r="G64" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H64" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I64" s="84" t="s">
+      <c r="H64" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I64" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J64" s="7" t="s">
@@ -14462,10 +14526,10 @@
       <c r="G65" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H65" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I65" s="84" t="s">
+      <c r="H65" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I65" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J65" s="7" t="s">
@@ -14562,10 +14626,10 @@
       <c r="G66" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H66" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I66" s="84" t="s">
+      <c r="H66" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I66" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J66" s="7" t="s">
@@ -14662,10 +14726,10 @@
       <c r="G67" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H67" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I67" s="84" t="s">
+      <c r="H67" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I67" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J67" s="7" t="s">
@@ -14762,10 +14826,10 @@
       <c r="G68" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H68" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I68" s="84" t="s">
+      <c r="H68" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I68" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J68" s="7" t="s">
@@ -14862,10 +14926,10 @@
       <c r="G69" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H69" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I69" s="84" t="s">
+      <c r="H69" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I69" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J69" s="7" t="s">
@@ -14962,10 +15026,10 @@
       <c r="G70" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H70" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I70" s="84" t="s">
+      <c r="H70" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I70" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J70" s="7" t="s">
@@ -15062,10 +15126,10 @@
       <c r="G71" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H71" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I71" s="84" t="s">
+      <c r="H71" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I71" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J71" s="7" t="s">
@@ -15162,10 +15226,10 @@
       <c r="G72" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H72" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I72" s="84" t="s">
+      <c r="H72" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I72" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J72" s="7" t="s">
@@ -15262,10 +15326,10 @@
       <c r="G73" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H73" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I73" s="84" t="s">
+      <c r="H73" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I73" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J73" s="7" t="s">
@@ -15362,10 +15426,10 @@
       <c r="G74" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H74" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I74" s="84" t="s">
+      <c r="H74" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I74" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J74" s="7" t="s">
@@ -15462,10 +15526,10 @@
       <c r="G75" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H75" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I75" s="84" t="s">
+      <c r="H75" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I75" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J75" s="7" t="s">
@@ -15562,10 +15626,10 @@
       <c r="G76" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H76" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I76" s="84" t="s">
+      <c r="H76" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I76" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J76" s="7" t="s">
@@ -15662,10 +15726,10 @@
       <c r="G77" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H77" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I77" s="84" t="s">
+      <c r="H77" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I77" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J77" s="7" t="s">
@@ -15762,10 +15826,10 @@
       <c r="G78" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H78" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I78" s="84" t="s">
+      <c r="H78" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I78" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J78" s="7" t="s">
@@ -15862,10 +15926,10 @@
       <c r="G79" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H79" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I79" s="84" t="s">
+      <c r="H79" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I79" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J79" s="7" t="s">
@@ -15962,10 +16026,10 @@
       <c r="G80" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H80" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I80" s="84" t="s">
+      <c r="H80" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I80" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J80" s="7" t="s">
@@ -16062,10 +16126,10 @@
       <c r="G81" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H81" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I81" s="84" t="s">
+      <c r="H81" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I81" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J81" s="7" t="s">
@@ -16162,10 +16226,10 @@
       <c r="G82" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H82" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I82" s="84" t="s">
+      <c r="H82" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I82" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J82" s="7" t="s">
@@ -16262,10 +16326,10 @@
       <c r="G83" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H83" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I83" s="84" t="s">
+      <c r="H83" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I83" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J83" s="7" t="s">
@@ -16362,10 +16426,10 @@
       <c r="G84" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H84" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I84" s="84" t="s">
+      <c r="H84" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I84" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J84" s="7" t="s">
@@ -16462,10 +16526,10 @@
       <c r="G85" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H85" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I85" s="84" t="s">
+      <c r="H85" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I85" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J85" s="7" t="s">
@@ -16562,10 +16626,10 @@
       <c r="G86" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H86" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I86" s="84" t="s">
+      <c r="H86" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I86" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J86" s="7" t="s">
@@ -16662,10 +16726,10 @@
       <c r="G87" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H87" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I87" s="84" t="s">
+      <c r="H87" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I87" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J87" s="7" t="s">
@@ -16762,10 +16826,10 @@
       <c r="G88" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H88" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I88" s="84" t="s">
+      <c r="H88" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I88" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J88" s="7" t="s">
@@ -16862,10 +16926,10 @@
       <c r="G89" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H89" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I89" s="84" t="s">
+      <c r="H89" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I89" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J89" s="7" t="s">
@@ -16962,10 +17026,10 @@
       <c r="G90" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H90" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I90" s="84" t="s">
+      <c r="H90" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I90" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J90" s="7" t="s">
@@ -17062,10 +17126,10 @@
       <c r="G91" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H91" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I91" s="84" t="s">
+      <c r="H91" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I91" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J91" s="7" t="s">
@@ -17162,10 +17226,10 @@
       <c r="G92" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H92" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I92" s="84" t="s">
+      <c r="H92" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I92" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J92" s="7" t="s">
@@ -17262,10 +17326,10 @@
       <c r="G93" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H93" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I93" s="84" t="s">
+      <c r="H93" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I93" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J93" s="7" t="s">
@@ -17362,10 +17426,10 @@
       <c r="G94" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H94" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I94" s="84" t="s">
+      <c r="H94" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I94" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J94" s="7" t="s">
@@ -17462,10 +17526,10 @@
       <c r="G95" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H95" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I95" s="84" t="s">
+      <c r="H95" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I95" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J95" s="7" t="s">
@@ -17562,10 +17626,10 @@
       <c r="G96" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H96" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I96" s="84" t="s">
+      <c r="H96" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I96" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J96" s="7" t="s">
@@ -17662,10 +17726,10 @@
       <c r="G97" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H97" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I97" s="84" t="s">
+      <c r="H97" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I97" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J97" s="7" t="s">
@@ -17762,10 +17826,10 @@
       <c r="G98" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H98" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I98" s="84" t="s">
+      <c r="H98" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I98" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J98" s="7" t="s">
@@ -17862,10 +17926,10 @@
       <c r="G99" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H99" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I99" s="84" t="s">
+      <c r="H99" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I99" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J99" s="7" t="s">
@@ -17962,10 +18026,10 @@
       <c r="G100" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H100" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I100" s="84" t="s">
+      <c r="H100" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I100" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J100" s="7" t="s">
@@ -18062,10 +18126,10 @@
       <c r="G101" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H101" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I101" s="84" t="s">
+      <c r="H101" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I101" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J101" s="7" t="s">
@@ -18162,10 +18226,10 @@
       <c r="G102" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H102" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I102" s="84" t="s">
+      <c r="H102" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I102" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J102" s="7" t="s">
@@ -18262,10 +18326,10 @@
       <c r="G103" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H103" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I103" s="84" t="s">
+      <c r="H103" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I103" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J103" s="7" t="s">
@@ -18362,10 +18426,10 @@
       <c r="G104" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H104" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I104" s="84" t="s">
+      <c r="H104" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I104" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J104" s="7" t="s">
@@ -18462,10 +18526,10 @@
       <c r="G105" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H105" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I105" s="84" t="s">
+      <c r="H105" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I105" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J105" s="7" t="s">
@@ -18562,10 +18626,10 @@
       <c r="G106" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H106" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I106" s="84" t="s">
+      <c r="H106" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I106" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J106" s="7" t="s">
@@ -18662,10 +18726,10 @@
       <c r="G107" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H107" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I107" s="84" t="s">
+      <c r="H107" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I107" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J107" s="7" t="s">
@@ -18762,10 +18826,10 @@
       <c r="G108" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H108" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I108" s="84" t="s">
+      <c r="H108" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I108" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J108" s="7" t="s">
@@ -18862,10 +18926,10 @@
       <c r="G109" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H109" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I109" s="84" t="s">
+      <c r="H109" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I109" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J109" s="7" t="s">
@@ -18962,10 +19026,10 @@
       <c r="G110" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H110" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I110" s="84" t="s">
+      <c r="H110" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I110" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J110" s="7" t="s">
@@ -19062,10 +19126,10 @@
       <c r="G111" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H111" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I111" s="84" t="s">
+      <c r="H111" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I111" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J111" s="7" t="s">
@@ -19162,10 +19226,10 @@
       <c r="G112" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H112" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I112" s="84" t="s">
+      <c r="H112" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I112" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J112" s="7" t="s">
@@ -19262,10 +19326,10 @@
       <c r="G113" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H113" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I113" s="84" t="s">
+      <c r="H113" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I113" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J113" s="7" t="s">
@@ -19362,10 +19426,10 @@
       <c r="G114" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H114" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I114" s="84" t="s">
+      <c r="H114" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I114" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J114" s="7" t="s">
@@ -19462,10 +19526,10 @@
       <c r="G115" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H115" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I115" s="84" t="s">
+      <c r="H115" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I115" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J115" s="7" t="s">
@@ -19562,10 +19626,10 @@
       <c r="G116" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H116" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I116" s="84" t="s">
+      <c r="H116" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I116" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J116" s="7" t="s">
@@ -19662,10 +19726,10 @@
       <c r="G117" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H117" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I117" s="84" t="s">
+      <c r="H117" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I117" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J117" s="7" t="s">
@@ -19762,10 +19826,10 @@
       <c r="G118" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H118" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I118" s="84" t="s">
+      <c r="H118" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I118" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J118" s="7" t="s">
@@ -19862,10 +19926,10 @@
       <c r="G119" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H119" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I119" s="84" t="s">
+      <c r="H119" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I119" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J119" s="7" t="s">
@@ -19962,10 +20026,10 @@
       <c r="G120" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H120" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I120" s="84" t="s">
+      <c r="H120" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I120" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J120" s="7" t="s">
@@ -20062,10 +20126,10 @@
       <c r="G121" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H121" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I121" s="84" t="s">
+      <c r="H121" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I121" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J121" s="7" t="s">
@@ -20162,10 +20226,10 @@
       <c r="G122" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H122" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I122" s="84" t="s">
+      <c r="H122" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I122" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J122" s="7" t="s">
@@ -20262,10 +20326,10 @@
       <c r="G123" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H123" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I123" s="84" t="s">
+      <c r="H123" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I123" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J123" s="7" t="s">
@@ -20362,10 +20426,10 @@
       <c r="G124" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H124" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I124" s="84" t="s">
+      <c r="H124" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I124" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J124" s="7" t="s">
@@ -20462,10 +20526,10 @@
       <c r="G125" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H125" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I125" s="84" t="s">
+      <c r="H125" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I125" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J125" s="7" t="s">
@@ -20562,10 +20626,10 @@
       <c r="G126" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H126" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I126" s="84" t="s">
+      <c r="H126" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I126" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J126" s="7" t="s">
@@ -20662,10 +20726,10 @@
       <c r="G127" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H127" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I127" s="84" t="s">
+      <c r="H127" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I127" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J127" s="7" t="s">
@@ -20762,10 +20826,10 @@
       <c r="G128" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H128" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I128" s="84" t="s">
+      <c r="H128" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I128" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J128" s="7" t="s">
@@ -20862,10 +20926,10 @@
       <c r="G129" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H129" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I129" s="84" t="s">
+      <c r="H129" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I129" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J129" s="7" t="s">
@@ -20962,10 +21026,10 @@
       <c r="G130" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H130" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I130" s="84" t="s">
+      <c r="H130" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I130" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J130" s="7" t="s">
@@ -21062,10 +21126,10 @@
       <c r="G131" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H131" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I131" s="84" t="s">
+      <c r="H131" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I131" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J131" s="7" t="s">
@@ -21162,10 +21226,10 @@
       <c r="G132" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H132" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I132" s="84" t="s">
+      <c r="H132" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I132" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J132" s="7" t="s">
@@ -21262,10 +21326,10 @@
       <c r="G133" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H133" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I133" s="84" t="s">
+      <c r="H133" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I133" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J133" s="7" t="s">
@@ -21362,10 +21426,10 @@
       <c r="G134" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H134" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I134" s="84" t="s">
+      <c r="H134" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I134" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J134" s="7" t="s">
@@ -21462,10 +21526,10 @@
       <c r="G135" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H135" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I135" s="84" t="s">
+      <c r="H135" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I135" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J135" s="7" t="s">
@@ -21562,10 +21626,10 @@
       <c r="G136" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H136" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I136" s="84" t="s">
+      <c r="H136" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I136" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J136" s="7" t="s">
@@ -21662,10 +21726,10 @@
       <c r="G137" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H137" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I137" s="84" t="s">
+      <c r="H137" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I137" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J137" s="7" t="s">
@@ -21762,10 +21826,10 @@
       <c r="G138" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H138" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I138" s="84" t="s">
+      <c r="H138" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I138" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J138" s="7" t="s">
@@ -21862,10 +21926,10 @@
       <c r="G139" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H139" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I139" s="84" t="s">
+      <c r="H139" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I139" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J139" s="7" t="s">
@@ -21962,10 +22026,10 @@
       <c r="G140" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H140" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I140" s="84" t="s">
+      <c r="H140" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I140" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J140" s="7" t="s">
@@ -22062,10 +22126,10 @@
       <c r="G141" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H141" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I141" s="84" t="s">
+      <c r="H141" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I141" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J141" s="7" t="s">
@@ -22162,10 +22226,10 @@
       <c r="G142" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H142" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I142" s="84" t="s">
+      <c r="H142" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I142" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J142" s="7" t="s">
@@ -22262,10 +22326,10 @@
       <c r="G143" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H143" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I143" s="84" t="s">
+      <c r="H143" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I143" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J143" s="7" t="s">
@@ -22362,10 +22426,10 @@
       <c r="G144" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H144" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I144" s="84" t="s">
+      <c r="H144" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I144" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J144" s="7" t="s">
@@ -22462,10 +22526,10 @@
       <c r="G145" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H145" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I145" s="84" t="s">
+      <c r="H145" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I145" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J145" s="7" t="s">
@@ -22562,10 +22626,10 @@
       <c r="G146" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H146" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I146" s="84" t="s">
+      <c r="H146" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I146" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J146" s="7" t="s">
@@ -22662,10 +22726,10 @@
       <c r="G147" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H147" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I147" s="84" t="s">
+      <c r="H147" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I147" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J147" s="7" t="s">
@@ -22762,10 +22826,10 @@
       <c r="G148" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H148" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I148" s="84" t="s">
+      <c r="H148" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I148" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J148" s="7" t="s">
@@ -22862,10 +22926,10 @@
       <c r="G149" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H149" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I149" s="84" t="s">
+      <c r="H149" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I149" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J149" s="7" t="s">
@@ -22962,10 +23026,10 @@
       <c r="G150" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H150" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I150" s="84" t="s">
+      <c r="H150" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I150" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J150" s="7" t="s">
@@ -23062,10 +23126,10 @@
       <c r="G151" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H151" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I151" s="84" t="s">
+      <c r="H151" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I151" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J151" s="7" t="s">
@@ -23162,10 +23226,10 @@
       <c r="G152" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H152" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I152" s="84" t="s">
+      <c r="H152" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I152" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J152" s="7" t="s">
@@ -23262,10 +23326,10 @@
       <c r="G153" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H153" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I153" s="84" t="s">
+      <c r="H153" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I153" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J153" s="7" t="s">
@@ -23362,10 +23426,10 @@
       <c r="G154" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H154" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I154" s="84" t="s">
+      <c r="H154" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I154" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J154" s="7" t="s">
@@ -23462,10 +23526,10 @@
       <c r="G155" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H155" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I155" s="84" t="s">
+      <c r="H155" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I155" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J155" s="7" t="s">
@@ -23562,10 +23626,10 @@
       <c r="G156" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H156" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I156" s="84" t="s">
+      <c r="H156" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I156" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J156" s="7" t="s">
@@ -23662,10 +23726,10 @@
       <c r="G157" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H157" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I157" s="84" t="s">
+      <c r="H157" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I157" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J157" s="7" t="s">
@@ -23762,10 +23826,10 @@
       <c r="G158" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H158" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I158" s="84" t="s">
+      <c r="H158" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I158" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J158" s="7" t="s">
@@ -23862,10 +23926,10 @@
       <c r="G159" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H159" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I159" s="84" t="s">
+      <c r="H159" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I159" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J159" s="7" t="s">
@@ -23962,10 +24026,10 @@
       <c r="G160" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H160" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I160" s="84" t="s">
+      <c r="H160" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I160" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J160" s="7" t="s">
@@ -24062,10 +24126,10 @@
       <c r="G161" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H161" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I161" s="84" t="s">
+      <c r="H161" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I161" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J161" s="7" t="s">
@@ -24162,10 +24226,10 @@
       <c r="G162" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H162" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I162" s="84" t="s">
+      <c r="H162" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I162" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J162" s="7" t="s">
@@ -24262,10 +24326,10 @@
       <c r="G163" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H163" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I163" s="84" t="s">
+      <c r="H163" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I163" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J163" s="7" t="s">
@@ -24362,10 +24426,10 @@
       <c r="G164" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H164" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I164" s="84" t="s">
+      <c r="H164" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I164" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J164" s="7" t="s">
@@ -24462,10 +24526,10 @@
       <c r="G165" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H165" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I165" s="84" t="s">
+      <c r="H165" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I165" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J165" s="7" t="s">
@@ -24562,10 +24626,10 @@
       <c r="G166" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H166" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I166" s="84" t="s">
+      <c r="H166" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I166" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J166" s="7" t="s">
@@ -24662,10 +24726,10 @@
       <c r="G167" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H167" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I167" s="84" t="s">
+      <c r="H167" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I167" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J167" s="7" t="s">
@@ -24762,10 +24826,10 @@
       <c r="G168" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H168" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I168" s="84" t="s">
+      <c r="H168" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I168" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J168" s="7" t="s">
@@ -24862,10 +24926,10 @@
       <c r="G169" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H169" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I169" s="84" t="s">
+      <c r="H169" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I169" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J169" s="7" t="s">
@@ -24962,10 +25026,10 @@
       <c r="G170" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H170" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I170" s="84" t="s">
+      <c r="H170" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I170" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J170" s="7" t="s">
@@ -25062,10 +25126,10 @@
       <c r="G171" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H171" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I171" s="84" t="s">
+      <c r="H171" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I171" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J171" s="7" t="s">
@@ -25162,10 +25226,10 @@
       <c r="G172" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H172" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I172" s="84" t="s">
+      <c r="H172" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I172" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J172" s="7" t="s">
@@ -25262,10 +25326,10 @@
       <c r="G173" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H173" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I173" s="84" t="s">
+      <c r="H173" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I173" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J173" s="7" t="s">
@@ -25362,10 +25426,10 @@
       <c r="G174" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H174" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I174" s="84" t="s">
+      <c r="H174" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I174" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J174" s="7" t="s">
@@ -25462,10 +25526,10 @@
       <c r="G175" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H175" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I175" s="84" t="s">
+      <c r="H175" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I175" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J175" s="7" t="s">
@@ -25562,10 +25626,10 @@
       <c r="G176" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H176" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I176" s="84" t="s">
+      <c r="H176" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I176" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J176" s="7" t="s">
@@ -25662,10 +25726,10 @@
       <c r="G177" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H177" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I177" s="84" t="s">
+      <c r="H177" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I177" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J177" s="7" t="s">
@@ -25762,10 +25826,10 @@
       <c r="G178" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H178" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I178" s="84" t="s">
+      <c r="H178" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I178" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J178" s="7" t="s">
@@ -25862,10 +25926,10 @@
       <c r="G179" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H179" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I179" s="84" t="s">
+      <c r="H179" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I179" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J179" s="7" t="s">
@@ -25962,10 +26026,10 @@
       <c r="G180" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H180" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I180" s="84" t="s">
+      <c r="H180" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I180" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J180" s="7" t="s">
@@ -26062,10 +26126,10 @@
       <c r="G181" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H181" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I181" s="84" t="s">
+      <c r="H181" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I181" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J181" s="7" t="s">
@@ -26162,10 +26226,10 @@
       <c r="G182" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H182" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I182" s="84" t="s">
+      <c r="H182" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I182" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J182" s="7" t="s">
@@ -26262,10 +26326,10 @@
       <c r="G183" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H183" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I183" s="84" t="s">
+      <c r="H183" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I183" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J183" s="7" t="s">
@@ -26362,10 +26426,10 @@
       <c r="G184" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H184" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I184" s="84" t="s">
+      <c r="H184" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I184" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J184" s="7" t="s">
@@ -26462,10 +26526,10 @@
       <c r="G185" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H185" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I185" s="84" t="s">
+      <c r="H185" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I185" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J185" s="7" t="s">
@@ -26562,10 +26626,10 @@
       <c r="G186" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H186" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I186" s="84" t="s">
+      <c r="H186" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I186" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J186" s="7" t="s">
@@ -26662,10 +26726,10 @@
       <c r="G187" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H187" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I187" s="84" t="s">
+      <c r="H187" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I187" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J187" s="7" t="s">
@@ -26762,10 +26826,10 @@
       <c r="G188" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H188" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I188" s="84" t="s">
+      <c r="H188" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I188" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J188" s="7" t="s">
@@ -26862,10 +26926,10 @@
       <c r="G189" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H189" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I189" s="84" t="s">
+      <c r="H189" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I189" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J189" s="7" t="s">
@@ -26962,10 +27026,10 @@
       <c r="G190" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H190" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I190" s="84" t="s">
+      <c r="H190" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I190" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J190" s="7" t="s">
@@ -27062,10 +27126,10 @@
       <c r="G191" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H191" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I191" s="84" t="s">
+      <c r="H191" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I191" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J191" s="7" t="s">
@@ -27162,10 +27226,10 @@
       <c r="G192" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H192" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I192" s="84" t="s">
+      <c r="H192" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I192" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J192" s="7" t="s">
@@ -27262,10 +27326,10 @@
       <c r="G193" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H193" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I193" s="84" t="s">
+      <c r="H193" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I193" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J193" s="7" t="s">
@@ -27362,10 +27426,10 @@
       <c r="G194" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H194" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I194" s="84" t="s">
+      <c r="H194" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I194" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J194" s="7" t="s">
@@ -27462,10 +27526,10 @@
       <c r="G195" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H195" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I195" s="84" t="s">
+      <c r="H195" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I195" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J195" s="7" t="s">
@@ -27562,10 +27626,10 @@
       <c r="G196" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H196" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I196" s="84" t="s">
+      <c r="H196" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I196" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J196" s="7" t="s">
@@ -27662,10 +27726,10 @@
       <c r="G197" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H197" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I197" s="84" t="s">
+      <c r="H197" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I197" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J197" s="7" t="s">
@@ -27762,10 +27826,10 @@
       <c r="G198" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H198" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I198" s="84" t="s">
+      <c r="H198" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I198" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J198" s="7" t="s">
@@ -27862,10 +27926,10 @@
       <c r="G199" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H199" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I199" s="84" t="s">
+      <c r="H199" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I199" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J199" s="7" t="s">
@@ -27962,10 +28026,10 @@
       <c r="G200" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H200" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I200" s="84" t="s">
+      <c r="H200" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I200" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J200" s="7" t="s">
@@ -28062,10 +28126,10 @@
       <c r="G201" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H201" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I201" s="84" t="s">
+      <c r="H201" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I201" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J201" s="7" t="s">
@@ -28162,10 +28226,10 @@
       <c r="G202" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H202" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I202" s="84" t="s">
+      <c r="H202" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I202" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J202" s="7" t="s">
@@ -28262,10 +28326,10 @@
       <c r="G203" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H203" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I203" s="84" t="s">
+      <c r="H203" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I203" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J203" s="7" t="s">
@@ -28362,10 +28426,10 @@
       <c r="G204" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H204" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I204" s="84" t="s">
+      <c r="H204" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I204" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J204" s="7" t="s">
@@ -28462,10 +28526,10 @@
       <c r="G205" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H205" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I205" s="84" t="s">
+      <c r="H205" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I205" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J205" s="7" t="s">
@@ -28562,10 +28626,10 @@
       <c r="G206" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H206" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I206" s="84" t="s">
+      <c r="H206" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I206" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J206" s="7" t="s">
@@ -28662,10 +28726,10 @@
       <c r="G207" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H207" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I207" s="84" t="s">
+      <c r="H207" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I207" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J207" s="7" t="s">
@@ -28762,10 +28826,10 @@
       <c r="G208" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H208" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I208" s="84" t="s">
+      <c r="H208" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I208" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J208" s="7" t="s">
@@ -28862,10 +28926,10 @@
       <c r="G209" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H209" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I209" s="84" t="s">
+      <c r="H209" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I209" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J209" s="7" t="s">
@@ -28962,10 +29026,10 @@
       <c r="G210" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H210" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I210" s="84" t="s">
+      <c r="H210" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I210" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J210" s="7" t="s">
@@ -29062,10 +29126,10 @@
       <c r="G211" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H211" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I211" s="84" t="s">
+      <c r="H211" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I211" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J211" s="7" t="s">
@@ -29162,10 +29226,10 @@
       <c r="G212" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H212" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I212" s="84" t="s">
+      <c r="H212" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I212" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J212" s="7" t="s">
@@ -29262,10 +29326,10 @@
       <c r="G213" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H213" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I213" s="84" t="s">
+      <c r="H213" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I213" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J213" s="7" t="s">
@@ -29362,10 +29426,10 @@
       <c r="G214" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H214" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I214" s="84" t="s">
+      <c r="H214" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I214" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J214" s="7" t="s">
@@ -29462,10 +29526,10 @@
       <c r="G215" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H215" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I215" s="84" t="s">
+      <c r="H215" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I215" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J215" s="7" t="s">
@@ -29562,10 +29626,10 @@
       <c r="G216" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H216" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I216" s="84" t="s">
+      <c r="H216" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I216" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J216" s="7" t="s">
@@ -29662,10 +29726,10 @@
       <c r="G217" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H217" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I217" s="84" t="s">
+      <c r="H217" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I217" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J217" s="7" t="s">
@@ -29762,10 +29826,10 @@
       <c r="G218" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H218" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I218" s="84" t="s">
+      <c r="H218" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I218" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J218" s="7" t="s">
@@ -29862,10 +29926,10 @@
       <c r="G219" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H219" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I219" s="84" t="s">
+      <c r="H219" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I219" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J219" s="7" t="s">
@@ -29962,10 +30026,10 @@
       <c r="G220" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H220" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I220" s="84" t="s">
+      <c r="H220" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I220" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J220" s="7" t="s">
@@ -30062,10 +30126,10 @@
       <c r="G221" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H221" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I221" s="84" t="s">
+      <c r="H221" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I221" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J221" s="7" t="s">
@@ -30162,10 +30226,10 @@
       <c r="G222" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H222" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I222" s="84" t="s">
+      <c r="H222" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I222" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J222" s="7" t="s">
@@ -30262,10 +30326,10 @@
       <c r="G223" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H223" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I223" s="84" t="s">
+      <c r="H223" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I223" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J223" s="7" t="s">
@@ -30362,10 +30426,10 @@
       <c r="G224" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H224" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I224" s="84" t="s">
+      <c r="H224" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I224" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J224" s="7" t="s">
@@ -30462,10 +30526,10 @@
       <c r="G225" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H225" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I225" s="84" t="s">
+      <c r="H225" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I225" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J225" s="7" t="s">
@@ -30562,10 +30626,10 @@
       <c r="G226" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H226" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I226" s="84" t="s">
+      <c r="H226" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I226" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J226" s="7" t="s">
@@ -30662,10 +30726,10 @@
       <c r="G227" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H227" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I227" s="84" t="s">
+      <c r="H227" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I227" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J227" s="7" t="s">
@@ -30762,10 +30826,10 @@
       <c r="G228" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H228" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I228" s="84" t="s">
+      <c r="H228" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I228" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J228" s="7" t="s">
@@ -30862,10 +30926,10 @@
       <c r="G229" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H229" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I229" s="84" t="s">
+      <c r="H229" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I229" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J229" s="7" t="s">
@@ -30962,10 +31026,10 @@
       <c r="G230" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H230" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I230" s="84" t="s">
+      <c r="H230" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I230" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J230" s="7" t="s">
@@ -31062,10 +31126,10 @@
       <c r="G231" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H231" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I231" s="84" t="s">
+      <c r="H231" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I231" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J231" s="7" t="s">
@@ -31162,10 +31226,10 @@
       <c r="G232" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H232" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I232" s="84" t="s">
+      <c r="H232" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I232" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J232" s="7" t="s">
@@ -31262,10 +31326,10 @@
       <c r="G233" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H233" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I233" s="84" t="s">
+      <c r="H233" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I233" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J233" s="7" t="s">
@@ -31362,10 +31426,10 @@
       <c r="G234" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H234" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I234" s="84" t="s">
+      <c r="H234" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I234" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J234" s="7" t="s">
@@ -31462,10 +31526,10 @@
       <c r="G235" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H235" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I235" s="84" t="s">
+      <c r="H235" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I235" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J235" s="7" t="s">
@@ -31562,10 +31626,10 @@
       <c r="G236" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H236" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I236" s="84" t="s">
+      <c r="H236" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I236" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J236" s="7" t="s">
@@ -31662,10 +31726,10 @@
       <c r="G237" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H237" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I237" s="84" t="s">
+      <c r="H237" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I237" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J237" s="7" t="s">
@@ -31762,10 +31826,10 @@
       <c r="G238" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H238" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I238" s="84" t="s">
+      <c r="H238" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I238" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J238" s="7" t="s">
@@ -31862,10 +31926,10 @@
       <c r="G239" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H239" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I239" s="84" t="s">
+      <c r="H239" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I239" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J239" s="7" t="s">
@@ -31962,10 +32026,10 @@
       <c r="G240" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H240" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I240" s="84" t="s">
+      <c r="H240" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I240" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J240" s="7" t="s">
@@ -32062,10 +32126,10 @@
       <c r="G241" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H241" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I241" s="84" t="s">
+      <c r="H241" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I241" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J241" s="7" t="s">
@@ -32162,10 +32226,10 @@
       <c r="G242" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H242" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I242" s="84" t="s">
+      <c r="H242" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I242" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J242" s="7" t="s">
@@ -32262,10 +32326,10 @@
       <c r="G243" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H243" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I243" s="84" t="s">
+      <c r="H243" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I243" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J243" s="7" t="s">
@@ -32362,10 +32426,10 @@
       <c r="G244" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H244" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I244" s="84" t="s">
+      <c r="H244" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I244" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J244" s="7" t="s">
@@ -32462,10 +32526,10 @@
       <c r="G245" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H245" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I245" s="84" t="s">
+      <c r="H245" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I245" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J245" s="7" t="s">
@@ -32562,10 +32626,10 @@
       <c r="G246" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H246" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I246" s="84" t="s">
+      <c r="H246" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I246" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J246" s="7" t="s">
@@ -32662,10 +32726,10 @@
       <c r="G247" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H247" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I247" s="84" t="s">
+      <c r="H247" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I247" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J247" s="7" t="s">
@@ -32762,10 +32826,10 @@
       <c r="G248" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H248" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I248" s="84" t="s">
+      <c r="H248" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I248" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J248" s="7" t="s">
@@ -32862,10 +32926,10 @@
       <c r="G249" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H249" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I249" s="84" t="s">
+      <c r="H249" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I249" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J249" s="7" t="s">
@@ -32962,10 +33026,10 @@
       <c r="G250" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H250" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I250" s="84" t="s">
+      <c r="H250" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I250" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J250" s="7" t="s">
@@ -33062,10 +33126,10 @@
       <c r="G251" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H251" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I251" s="84" t="s">
+      <c r="H251" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I251" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J251" s="7" t="s">
@@ -33162,10 +33226,10 @@
       <c r="G252" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H252" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I252" s="84" t="s">
+      <c r="H252" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I252" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J252" s="7" t="s">
@@ -33262,10 +33326,10 @@
       <c r="G253" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H253" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I253" s="84" t="s">
+      <c r="H253" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I253" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J253" s="7" t="s">
@@ -33362,10 +33426,10 @@
       <c r="G254" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H254" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I254" s="84" t="s">
+      <c r="H254" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I254" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J254" s="7" t="s">
@@ -33462,10 +33526,10 @@
       <c r="G255" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H255" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I255" s="84" t="s">
+      <c r="H255" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I255" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J255" s="7" t="s">
@@ -33562,10 +33626,10 @@
       <c r="G256" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H256" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I256" s="84" t="s">
+      <c r="H256" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I256" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J256" s="7" t="s">
@@ -33662,10 +33726,10 @@
       <c r="G257" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H257" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I257" s="84" t="s">
+      <c r="H257" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I257" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J257" s="7" t="s">
@@ -33762,10 +33826,10 @@
       <c r="G258" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H258" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I258" s="84" t="s">
+      <c r="H258" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I258" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J258" s="7" t="s">
@@ -33862,10 +33926,10 @@
       <c r="G259" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H259" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I259" s="84" t="s">
+      <c r="H259" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I259" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J259" s="7" t="s">
@@ -33962,10 +34026,10 @@
       <c r="G260" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H260" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I260" s="84" t="s">
+      <c r="H260" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I260" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J260" s="7" t="s">
@@ -34062,10 +34126,10 @@
       <c r="G261" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H261" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I261" s="84" t="s">
+      <c r="H261" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I261" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J261" s="7" t="s">
@@ -34162,10 +34226,10 @@
       <c r="G262" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H262" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I262" s="84" t="s">
+      <c r="H262" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I262" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J262" s="7" t="s">
@@ -34262,10 +34326,10 @@
       <c r="G263" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H263" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I263" s="84" t="s">
+      <c r="H263" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I263" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J263" s="7" t="s">
@@ -34362,10 +34426,10 @@
       <c r="G264" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H264" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I264" s="84" t="s">
+      <c r="H264" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I264" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J264" s="7" t="s">
@@ -34462,10 +34526,10 @@
       <c r="G265" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H265" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I265" s="84" t="s">
+      <c r="H265" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I265" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J265" s="7" t="s">
@@ -34562,10 +34626,10 @@
       <c r="G266" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H266" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I266" s="84" t="s">
+      <c r="H266" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I266" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J266" s="7" t="s">
@@ -34662,10 +34726,10 @@
       <c r="G267" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H267" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I267" s="84" t="s">
+      <c r="H267" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I267" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J267" s="7" t="s">
@@ -34762,10 +34826,10 @@
       <c r="G268" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H268" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I268" s="84" t="s">
+      <c r="H268" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I268" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J268" s="7" t="s">
@@ -34862,10 +34926,10 @@
       <c r="G269" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H269" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I269" s="84" t="s">
+      <c r="H269" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I269" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J269" s="7" t="s">
@@ -35062,7 +35126,7 @@
       <c r="G271" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H271" s="84" t="s">
+      <c r="H271" s="83" t="s">
         <v>9</v>
       </c>
       <c r="I271" s="7" t="s">
@@ -35162,7 +35226,7 @@
       <c r="G272" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H272" s="84" t="s">
+      <c r="H272" s="83" t="s">
         <v>9</v>
       </c>
       <c r="I272" s="7" t="s">
@@ -35362,10 +35426,10 @@
       <c r="G274" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H274" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I274" s="84" t="s">
+      <c r="H274" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I274" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J274" s="7" t="s">
@@ -35462,10 +35526,10 @@
       <c r="G275" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H275" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I275" s="84" t="s">
+      <c r="H275" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I275" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J275" s="7" t="s">
@@ -35562,10 +35626,10 @@
       <c r="G276" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H276" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I276" s="84" t="s">
+      <c r="H276" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I276" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J276" s="7" t="s">
@@ -35662,10 +35726,10 @@
       <c r="G277" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H277" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I277" s="84" t="s">
+      <c r="H277" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I277" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J277" s="7" t="s">
@@ -35762,10 +35826,10 @@
       <c r="G278" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H278" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I278" s="84" t="s">
+      <c r="H278" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I278" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J278" s="7" t="s">
@@ -35862,10 +35926,10 @@
       <c r="G279" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H279" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I279" s="84" t="s">
+      <c r="H279" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I279" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J279" s="7" t="s">
@@ -36062,10 +36126,10 @@
       <c r="G281" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H281" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I281" s="84" t="s">
+      <c r="H281" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I281" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J281" s="7" t="s">
@@ -36162,10 +36226,10 @@
       <c r="G282" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H282" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I282" s="84" t="s">
+      <c r="H282" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I282" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J282" s="7" t="s">
@@ -36262,10 +36326,10 @@
       <c r="G283" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H283" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I283" s="84" t="s">
+      <c r="H283" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I283" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J283" s="7" t="s">
@@ -36362,10 +36426,10 @@
       <c r="G284" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H284" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I284" s="84" t="s">
+      <c r="H284" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I284" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J284" s="7" t="s">
@@ -36462,10 +36526,10 @@
       <c r="G285" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H285" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I285" s="84" t="s">
+      <c r="H285" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I285" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J285" s="7" t="s">
@@ -36562,10 +36626,10 @@
       <c r="G286" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H286" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I286" s="84" t="s">
+      <c r="H286" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I286" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J286" s="7" t="s">
@@ -36662,10 +36726,10 @@
       <c r="G287" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H287" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I287" s="84" t="s">
+      <c r="H287" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I287" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J287" s="7" t="s">
@@ -36762,10 +36826,10 @@
       <c r="G288" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H288" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I288" s="84" t="s">
+      <c r="H288" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I288" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J288" s="7" t="s">
@@ -36862,10 +36926,10 @@
       <c r="G289" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H289" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I289" s="84" t="s">
+      <c r="H289" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I289" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J289" s="7" t="s">
@@ -36962,10 +37026,10 @@
       <c r="G290" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H290" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I290" s="84" t="s">
+      <c r="H290" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I290" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J290" s="7" t="s">
@@ -37062,10 +37126,10 @@
       <c r="G291" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H291" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I291" s="84" t="s">
+      <c r="H291" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I291" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J291" s="7" t="s">
@@ -37162,10 +37226,10 @@
       <c r="G292" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H292" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I292" s="84" t="s">
+      <c r="H292" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I292" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J292" s="7" t="s">
@@ -37262,10 +37326,10 @@
       <c r="G293" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H293" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I293" s="84" t="s">
+      <c r="H293" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I293" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J293" s="7" t="s">
@@ -37362,10 +37426,10 @@
       <c r="G294" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H294" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I294" s="84" t="s">
+      <c r="H294" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I294" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J294" s="7" t="s">
@@ -37462,10 +37526,10 @@
       <c r="G295" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H295" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I295" s="84" t="s">
+      <c r="H295" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I295" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J295" s="7" t="s">
@@ -37562,10 +37626,10 @@
       <c r="G296" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H296" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I296" s="84" t="s">
+      <c r="H296" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I296" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J296" s="7" t="s">
@@ -37662,10 +37726,10 @@
       <c r="G297" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H297" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I297" s="84" t="s">
+      <c r="H297" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I297" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J297" s="7" t="s">
@@ -37762,10 +37826,10 @@
       <c r="G298" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H298" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I298" s="84" t="s">
+      <c r="H298" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I298" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J298" s="7" t="s">
@@ -37862,10 +37926,10 @@
       <c r="G299" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H299" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I299" s="84" t="s">
+      <c r="H299" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I299" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J299" s="7" t="s">
@@ -37962,10 +38026,10 @@
       <c r="G300" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H300" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I300" s="84" t="s">
+      <c r="H300" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I300" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J300" s="7" t="s">
@@ -38062,10 +38126,10 @@
       <c r="G301" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H301" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I301" s="84" t="s">
+      <c r="H301" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I301" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J301" s="7" t="s">
@@ -38162,10 +38226,10 @@
       <c r="G302" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H302" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I302" s="84" t="s">
+      <c r="H302" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I302" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J302" s="7" t="s">
@@ -38262,10 +38326,10 @@
       <c r="G303" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H303" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I303" s="84" t="s">
+      <c r="H303" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I303" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J303" s="7" t="s">
@@ -38362,10 +38426,10 @@
       <c r="G304" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H304" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I304" s="84" t="s">
+      <c r="H304" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I304" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J304" s="7" t="s">
@@ -38462,10 +38526,10 @@
       <c r="G305" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H305" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I305" s="84" t="s">
+      <c r="H305" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I305" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J305" s="7" t="s">
@@ -38562,10 +38626,10 @@
       <c r="G306" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H306" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I306" s="84" t="s">
+      <c r="H306" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I306" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J306" s="7" t="s">
@@ -38662,10 +38726,10 @@
       <c r="G307" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H307" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I307" s="84" t="s">
+      <c r="H307" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I307" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J307" s="7" t="s">
@@ -38762,10 +38826,10 @@
       <c r="G308" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H308" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I308" s="84" t="s">
+      <c r="H308" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I308" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J308" s="7" t="s">
@@ -38862,10 +38926,10 @@
       <c r="G309" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H309" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I309" s="84" t="s">
+      <c r="H309" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I309" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J309" s="7" t="s">
@@ -38962,10 +39026,10 @@
       <c r="G310" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H310" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I310" s="84" t="s">
+      <c r="H310" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I310" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J310" s="7" t="s">
@@ -39062,10 +39126,10 @@
       <c r="G311" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H311" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I311" s="84" t="s">
+      <c r="H311" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I311" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J311" s="7" t="s">
@@ -39162,10 +39226,10 @@
       <c r="G312" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H312" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I312" s="84" t="s">
+      <c r="H312" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I312" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J312" s="7" t="s">
@@ -39262,10 +39326,10 @@
       <c r="G313" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H313" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I313" s="84" t="s">
+      <c r="H313" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I313" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J313" s="7" t="s">
@@ -39362,10 +39426,10 @@
       <c r="G314" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H314" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I314" s="84" t="s">
+      <c r="H314" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I314" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J314" s="7" t="s">
@@ -39462,10 +39526,10 @@
       <c r="G315" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H315" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I315" s="84" t="s">
+      <c r="H315" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I315" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J315" s="7" t="s">
@@ -39562,10 +39626,10 @@
       <c r="G316" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H316" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I316" s="84" t="s">
+      <c r="H316" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I316" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J316" s="7" t="s">
@@ -39662,10 +39726,10 @@
       <c r="G317" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H317" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I317" s="84" t="s">
+      <c r="H317" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I317" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J317" s="7" t="s">
@@ -39763,10 +39827,10 @@
       <c r="G318" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H318" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I318" s="84" t="s">
+      <c r="H318" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I318" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J318" s="7" t="s">
@@ -39864,10 +39928,10 @@
       <c r="G319" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H319" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I319" s="84" t="s">
+      <c r="H319" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I319" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J319" s="7" t="s">
@@ -39965,10 +40029,10 @@
       <c r="G320" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H320" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I320" s="84" t="s">
+      <c r="H320" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I320" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J320" s="7" t="s">
@@ -40022,7 +40086,7 @@
         <v>81</v>
       </c>
       <c r="X320" s="57" t="str">
-        <f t="shared" ref="X320:X350" si="80">CONCATENATE("Key-ARQ-",A320)</f>
+        <f t="shared" ref="X320:X355" si="80">CONCATENATE("Key-ARQ-",A320)</f>
         <v>Key-ARQ-320</v>
       </c>
       <c r="Y320" s="19" t="s">
@@ -40066,10 +40130,10 @@
       <c r="G321" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H321" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I321" s="84" t="s">
+      <c r="H321" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I321" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J321" s="7" t="s">
@@ -40167,10 +40231,10 @@
       <c r="G322" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H322" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I322" s="84" t="s">
+      <c r="H322" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I322" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J322" s="7" t="s">
@@ -40268,10 +40332,10 @@
       <c r="G323" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H323" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I323" s="84" t="s">
+      <c r="H323" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I323" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J323" s="7" t="s">
@@ -40369,10 +40433,10 @@
       <c r="G324" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H324" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I324" s="84" t="s">
+      <c r="H324" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I324" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J324" s="7" t="s">
@@ -40470,10 +40534,10 @@
       <c r="G325" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H325" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I325" s="84" t="s">
+      <c r="H325" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I325" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J325" s="7" t="s">
@@ -40571,10 +40635,10 @@
       <c r="G326" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H326" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I326" s="84" t="s">
+      <c r="H326" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I326" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J326" s="7" t="s">
@@ -40672,10 +40736,10 @@
       <c r="G327" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H327" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I327" s="84" t="s">
+      <c r="H327" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I327" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J327" s="7" t="s">
@@ -40773,10 +40837,10 @@
       <c r="G328" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H328" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I328" s="84" t="s">
+      <c r="H328" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I328" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J328" s="7" t="s">
@@ -40874,10 +40938,10 @@
       <c r="G329" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H329" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I329" s="84" t="s">
+      <c r="H329" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I329" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J329" s="7" t="s">
@@ -40975,10 +41039,10 @@
       <c r="G330" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H330" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I330" s="84" t="s">
+      <c r="H330" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I330" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J330" s="7" t="s">
@@ -41075,10 +41139,10 @@
       <c r="G331" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H331" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I331" s="84" t="s">
+      <c r="H331" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I331" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J331" s="7" t="s">
@@ -41175,10 +41239,10 @@
       <c r="G332" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H332" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I332" s="84" t="s">
+      <c r="H332" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I332" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J332" s="7" t="s">
@@ -41275,10 +41339,10 @@
       <c r="G333" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H333" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I333" s="84" t="s">
+      <c r="H333" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I333" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J333" s="7" t="s">
@@ -41375,10 +41439,10 @@
       <c r="G334" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H334" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I334" s="84" t="s">
+      <c r="H334" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I334" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J334" s="7" t="s">
@@ -41475,10 +41539,10 @@
       <c r="G335" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H335" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I335" s="84" t="s">
+      <c r="H335" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I335" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J335" s="7" t="s">
@@ -41575,10 +41639,10 @@
       <c r="G336" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H336" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I336" s="84" t="s">
+      <c r="H336" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I336" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J336" s="7" t="s">
@@ -41675,10 +41739,10 @@
       <c r="G337" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H337" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I337" s="84" t="s">
+      <c r="H337" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I337" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J337" s="7" t="s">
@@ -41775,10 +41839,10 @@
       <c r="G338" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H338" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I338" s="84" t="s">
+      <c r="H338" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I338" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J338" s="7" t="s">
@@ -41875,10 +41939,10 @@
       <c r="G339" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H339" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I339" s="84" t="s">
+      <c r="H339" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I339" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J339" s="7" t="s">
@@ -41975,10 +42039,10 @@
       <c r="G340" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H340" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I340" s="84" t="s">
+      <c r="H340" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I340" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J340" s="7" t="s">
@@ -42075,10 +42139,10 @@
       <c r="G341" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H341" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I341" s="84" t="s">
+      <c r="H341" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I341" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J341" s="7" t="s">
@@ -42175,10 +42239,10 @@
       <c r="G342" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H342" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I342" s="84" t="s">
+      <c r="H342" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I342" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J342" s="7" t="s">
@@ -42276,10 +42340,10 @@
       <c r="G343" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H343" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I343" s="84" t="s">
+      <c r="H343" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I343" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J343" s="7" t="s">
@@ -42377,10 +42441,10 @@
       <c r="G344" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H344" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I344" s="84" t="s">
+      <c r="H344" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I344" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J344" s="7" t="s">
@@ -42478,10 +42542,10 @@
       <c r="G345" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H345" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I345" s="84" t="s">
+      <c r="H345" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I345" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J345" s="7" t="s">
@@ -42579,10 +42643,10 @@
       <c r="G346" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H346" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I346" s="84" t="s">
+      <c r="H346" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I346" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J346" s="7" t="s">
@@ -42680,10 +42744,10 @@
       <c r="G347" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H347" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I347" s="84" t="s">
+      <c r="H347" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I347" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J347" s="7" t="s">
@@ -42781,10 +42845,10 @@
       <c r="G348" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H348" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I348" s="84" t="s">
+      <c r="H348" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I348" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J348" s="7" t="s">
@@ -42882,10 +42946,10 @@
       <c r="G349" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H349" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I349" s="84" t="s">
+      <c r="H349" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I349" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J349" s="7" t="s">
@@ -42983,10 +43047,10 @@
       <c r="G350" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H350" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I350" s="84" t="s">
+      <c r="H350" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I350" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J350" s="7" t="s">
@@ -43062,185 +43126,171 @@
         <v>9</v>
       </c>
     </row>
-    <row r="351" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:30" s="87" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="21">
         <v>351</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>43</v>
+        <v>2029</v>
       </c>
       <c r="C351" s="71" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D351" s="71" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E351" s="71" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F351" s="71" t="s">
         <v>2008</v>
       </c>
-      <c r="D351" s="71" t="s">
+      <c r="G351" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="H351" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="I351" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="J351" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="K351" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="L351" s="24" t="s">
+        <v>2030</v>
+      </c>
+      <c r="M351" s="24" t="s">
+        <v>2031</v>
+      </c>
+      <c r="N351" s="24" t="s">
+        <v>2033</v>
+      </c>
+      <c r="O351" s="24" t="s">
+        <v>2034</v>
+      </c>
+      <c r="P351" s="19" t="s">
+        <v>2009</v>
+      </c>
+      <c r="Q351" s="19" t="s">
         <v>2010</v>
       </c>
-      <c r="E351" s="71" t="s">
-        <v>2009</v>
-      </c>
-      <c r="F351" s="71" t="s">
+      <c r="R351" s="19" t="s">
         <v>2011</v>
       </c>
-      <c r="G351" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="H351" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="I351" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="J351" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="K351" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="L351" s="24" t="str">
-        <f t="shared" ref="L351:O355" si="82">SUBSTITUTE(CONCATENATE("", C351), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M351" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Macros</v>
-      </c>
-      <c r="N351" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O351" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P351" s="19" t="s">
-        <v>2012</v>
-      </c>
-      <c r="Q351" s="19" t="s">
-        <v>2013</v>
-      </c>
-      <c r="R351" s="19" t="s">
-        <v>2014</v>
-      </c>
       <c r="S351" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="T351" s="19" t="str">
-        <f t="shared" si="77"/>
-        <v>De API</v>
-      </c>
-      <c r="U351" s="19" t="str">
-        <f t="shared" si="77"/>
-        <v>Macros</v>
-      </c>
-      <c r="V351" s="25" t="str">
-        <f t="shared" si="77"/>
-        <v>Métodos</v>
+      <c r="T351" s="19" t="s">
+        <v>2035</v>
+      </c>
+      <c r="U351" s="19" t="s">
+        <v>2036</v>
+      </c>
+      <c r="V351" s="25" t="s">
+        <v>2033</v>
       </c>
       <c r="W351" s="19" t="s">
         <v>81</v>
       </c>
       <c r="X351" s="57" t="str">
-        <f t="shared" ref="X351:X355" si="83">CONCATENATE("Key-ARQ-",A351)</f>
+        <f t="shared" si="80"/>
         <v>Key-ARQ-351</v>
       </c>
       <c r="Y351" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="Z351" s="25" t="s">
+      <c r="Z351" s="80" t="s">
         <v>9</v>
       </c>
       <c r="AA351" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="AB351" s="25" t="s">
+      <c r="AB351" s="80" t="s">
         <v>9</v>
       </c>
       <c r="AC351" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="AD351" s="25" t="s">
+      <c r="AD351" s="80" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="352" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:30" s="87" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="21">
         <v>352</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>43</v>
+        <v>2029</v>
       </c>
       <c r="C352" s="71" t="s">
-        <v>2008</v>
+        <v>2030</v>
       </c>
       <c r="D352" s="71" t="s">
-        <v>2010</v>
+        <v>2031</v>
       </c>
       <c r="E352" s="71" t="s">
-        <v>2009</v>
+        <v>2032</v>
       </c>
       <c r="F352" s="71" t="s">
+        <v>2012</v>
+      </c>
+      <c r="G352" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="H352" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="I352" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="J352" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="K352" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="L352" s="24" t="s">
+        <v>2030</v>
+      </c>
+      <c r="M352" s="24" t="s">
+        <v>2031</v>
+      </c>
+      <c r="N352" s="24" t="s">
+        <v>2033</v>
+      </c>
+      <c r="O352" s="24" t="s">
+        <v>2037</v>
+      </c>
+      <c r="P352" s="19" t="s">
+        <v>2013</v>
+      </c>
+      <c r="Q352" s="19" t="s">
+        <v>2014</v>
+      </c>
+      <c r="R352" s="19" t="s">
         <v>2015</v>
       </c>
-      <c r="G352" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="H352" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="I352" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="J352" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="K352" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="L352" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>De API</v>
-      </c>
-      <c r="M352" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Macros</v>
-      </c>
-      <c r="N352" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O352" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P352" s="19" t="s">
-        <v>2016</v>
-      </c>
-      <c r="Q352" s="19" t="s">
-        <v>2017</v>
-      </c>
-      <c r="R352" s="19" t="s">
-        <v>2018</v>
-      </c>
       <c r="S352" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="T352" s="19" t="str">
-        <f t="shared" ref="T352:V355" si="84">SUBSTITUTE(C352, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U352" s="19" t="str">
-        <f t="shared" si="84"/>
-        <v>Macros</v>
-      </c>
-      <c r="V352" s="25" t="str">
-        <f t="shared" si="84"/>
-        <v>Métodos</v>
+      <c r="T352" s="19" t="s">
+        <v>2035</v>
+      </c>
+      <c r="U352" s="19" t="s">
+        <v>2036</v>
+      </c>
+      <c r="V352" s="25" t="s">
+        <v>2033</v>
       </c>
       <c r="W352" s="19" t="s">
         <v>81</v>
       </c>
       <c r="X352" s="57" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>Key-ARQ-352</v>
       </c>
       <c r="Y352" s="80" t="s">
@@ -43262,85 +43312,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="353" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:30" s="87" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="21">
         <v>353</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>43</v>
+        <v>2029</v>
       </c>
       <c r="C353" s="71" t="s">
-        <v>2008</v>
+        <v>2030</v>
       </c>
       <c r="D353" s="71" t="s">
-        <v>2010</v>
+        <v>2031</v>
       </c>
       <c r="E353" s="71" t="s">
-        <v>2009</v>
+        <v>2032</v>
       </c>
       <c r="F353" s="71" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G353" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="H353" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="I353" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="J353" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="K353" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="L353" s="24" t="s">
+        <v>2030</v>
+      </c>
+      <c r="M353" s="24" t="s">
+        <v>2031</v>
+      </c>
+      <c r="N353" s="24" t="s">
+        <v>2033</v>
+      </c>
+      <c r="O353" s="24" t="s">
+        <v>2038</v>
+      </c>
+      <c r="P353" s="19" t="s">
+        <v>2017</v>
+      </c>
+      <c r="Q353" s="19" t="s">
+        <v>2018</v>
+      </c>
+      <c r="R353" s="19" t="s">
         <v>2019</v>
       </c>
-      <c r="G353" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="H353" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="I353" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="J353" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="K353" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="L353" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>De API</v>
-      </c>
-      <c r="M353" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Macros</v>
-      </c>
-      <c r="N353" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O353" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P353" s="19" t="s">
-        <v>2020</v>
-      </c>
-      <c r="Q353" s="19" t="s">
-        <v>2021</v>
-      </c>
-      <c r="R353" s="19" t="s">
-        <v>2022</v>
-      </c>
       <c r="S353" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="T353" s="19" t="str">
-        <f t="shared" si="84"/>
-        <v>De API</v>
-      </c>
-      <c r="U353" s="19" t="str">
-        <f t="shared" si="84"/>
-        <v>Macros</v>
-      </c>
-      <c r="V353" s="25" t="str">
-        <f t="shared" si="84"/>
-        <v>Métodos</v>
+      <c r="T353" s="19" t="s">
+        <v>2035</v>
+      </c>
+      <c r="U353" s="19" t="s">
+        <v>2036</v>
+      </c>
+      <c r="V353" s="25" t="s">
+        <v>2033</v>
       </c>
       <c r="W353" s="19" t="s">
         <v>81</v>
       </c>
       <c r="X353" s="57" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>Key-ARQ-353</v>
       </c>
       <c r="Y353" s="80" t="s">
@@ -43362,85 +43405,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="354" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:30" s="87" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="21">
         <v>354</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>43</v>
+        <v>2029</v>
       </c>
       <c r="C354" s="71" t="s">
-        <v>2008</v>
+        <v>2030</v>
       </c>
       <c r="D354" s="71" t="s">
-        <v>2010</v>
+        <v>2031</v>
       </c>
       <c r="E354" s="71" t="s">
-        <v>2009</v>
+        <v>2032</v>
       </c>
       <c r="F354" s="71" t="s">
+        <v>2020</v>
+      </c>
+      <c r="G354" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="H354" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="I354" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="J354" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="K354" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="L354" s="24" t="s">
+        <v>2030</v>
+      </c>
+      <c r="M354" s="24" t="s">
+        <v>2031</v>
+      </c>
+      <c r="N354" s="24" t="s">
+        <v>2033</v>
+      </c>
+      <c r="O354" s="24" t="s">
+        <v>2039</v>
+      </c>
+      <c r="P354" s="19" t="s">
+        <v>2021</v>
+      </c>
+      <c r="Q354" s="19" t="s">
+        <v>2022</v>
+      </c>
+      <c r="R354" s="19" t="s">
         <v>2023</v>
       </c>
-      <c r="G354" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="H354" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="I354" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="J354" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="K354" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="L354" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>De API</v>
-      </c>
-      <c r="M354" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Macros</v>
-      </c>
-      <c r="N354" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O354" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P354" s="19" t="s">
-        <v>2024</v>
-      </c>
-      <c r="Q354" s="19" t="s">
-        <v>2025</v>
-      </c>
-      <c r="R354" s="19" t="s">
-        <v>2026</v>
-      </c>
       <c r="S354" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="T354" s="19" t="str">
-        <f t="shared" si="84"/>
-        <v>De API</v>
-      </c>
-      <c r="U354" s="19" t="str">
-        <f t="shared" si="84"/>
-        <v>Macros</v>
-      </c>
-      <c r="V354" s="25" t="str">
-        <f t="shared" si="84"/>
-        <v>Métodos</v>
+      <c r="T354" s="19" t="s">
+        <v>2035</v>
+      </c>
+      <c r="U354" s="19" t="s">
+        <v>2036</v>
+      </c>
+      <c r="V354" s="25" t="s">
+        <v>2033</v>
       </c>
       <c r="W354" s="19" t="s">
         <v>81</v>
       </c>
       <c r="X354" s="57" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>Key-ARQ-354</v>
       </c>
       <c r="Y354" s="80" t="s">
@@ -43462,85 +43498,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="355" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:30" s="87" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="21">
         <v>355</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>43</v>
+        <v>2029</v>
       </c>
       <c r="C355" s="71" t="s">
-        <v>2008</v>
+        <v>2030</v>
       </c>
       <c r="D355" s="71" t="s">
-        <v>2010</v>
+        <v>2040</v>
       </c>
       <c r="E355" s="71" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F355" s="71" t="s">
+        <v>2024</v>
+      </c>
+      <c r="G355" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="H355" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="I355" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="J355" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="K355" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="L355" s="24" t="s">
+        <v>2030</v>
+      </c>
+      <c r="M355" s="24" t="s">
+        <v>2040</v>
+      </c>
+      <c r="N355" s="24" t="s">
+        <v>2042</v>
+      </c>
+      <c r="O355" s="24" t="s">
+        <v>2043</v>
+      </c>
+      <c r="P355" s="19" t="s">
+        <v>2025</v>
+      </c>
+      <c r="Q355" s="19" t="s">
+        <v>2026</v>
+      </c>
+      <c r="R355" s="19" t="s">
         <v>2027</v>
       </c>
-      <c r="F355" s="71" t="s">
-        <v>2028</v>
-      </c>
-      <c r="G355" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="H355" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="I355" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="J355" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="K355" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="L355" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>De API</v>
-      </c>
-      <c r="M355" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Macros</v>
-      </c>
-      <c r="N355" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O355" s="24" t="str">
-        <f t="shared" si="82"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P355" s="19" t="s">
-        <v>2029</v>
-      </c>
-      <c r="Q355" s="19" t="s">
-        <v>2030</v>
-      </c>
-      <c r="R355" s="19" t="s">
-        <v>2031</v>
-      </c>
       <c r="S355" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="T355" s="19" t="str">
-        <f t="shared" si="84"/>
-        <v>De API</v>
-      </c>
-      <c r="U355" s="19" t="str">
-        <f t="shared" si="84"/>
-        <v>Macros</v>
-      </c>
-      <c r="V355" s="25" t="str">
-        <f t="shared" si="84"/>
-        <v>Códigos Visuais</v>
+      <c r="T355" s="19" t="s">
+        <v>2035</v>
+      </c>
+      <c r="U355" s="19" t="s">
+        <v>2044</v>
+      </c>
+      <c r="V355" s="25" t="s">
+        <v>2042</v>
       </c>
       <c r="W355" s="19" t="s">
         <v>81</v>
       </c>
       <c r="X355" s="57" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>Key-ARQ-355</v>
       </c>
       <c r="Y355" s="80" t="s">
@@ -43567,53 +43596,46 @@
     <sortCondition ref="A1:A350"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A351:B355">
-    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E355:F355">
-    <cfRule type="duplicateValues" dxfId="50" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F350 F356:F1048576">
-    <cfRule type="duplicateValues" dxfId="49" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17:F36">
-    <cfRule type="duplicateValues" dxfId="48" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F270">
-    <cfRule type="duplicateValues" dxfId="47" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F271:F272 F274:F279 F1:F16 F281:F350 F37:F269 F356:F1048576">
-    <cfRule type="duplicateValues" dxfId="46" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F271:F272 F274:F279 F281:F350 F1:F269 F356:F1048576">
-    <cfRule type="duplicateValues" dxfId="45" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F273">
-    <cfRule type="duplicateValues" dxfId="44" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F280">
-    <cfRule type="duplicateValues" dxfId="43" priority="543"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F351:F354">
-    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F356:F1048576">
-    <cfRule type="duplicateValues" dxfId="41" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="673"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:X1 AA1:AA342 A1:F350 L1:R350 AE1:XFD350 T2:W350 W351:W355 A356:F1048576 L356:X1048576 AE356:XFD1048576">
-    <cfRule type="cellIs" dxfId="40" priority="23" operator="equal">
+  <conditionalFormatting sqref="S1:X1 AA1:AA342 A1:F350 L1:R350 AE1:XFD350 T2:W349 A356:F1048576 L356:X1048576 AE356:XFD1048576 A351:A355 T350:V350 W350:W355">
+    <cfRule type="cellIs" dxfId="0" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X356:X1048576 X1">
-    <cfRule type="duplicateValues" dxfId="39" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA344:AA350 AA356:AA1048576">
-    <cfRule type="cellIs" dxfId="38" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F351:F355">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -43762,7 +43784,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43834,15 +43856,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B2:G1048576">
-    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="40" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="34" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -43854,7 +43876,7 @@
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" style="42" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" style="42" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.85546875" style="42" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.85546875" style="42" bestFit="1" customWidth="1"/>
@@ -63587,106 +63609,106 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1 B2:B31 B113:B132 A133:B1048576 D1:I1048576 L1:XFD124 A2:A132 T125:AO125 T126:XFD126 T127:AS127 AT127:XFD129 T128:AP129 AR128:AS129 T130:XFD131 L132:XFD1048576">
-    <cfRule type="cellIs" dxfId="33" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="88" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B31 B113:B1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="31" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:B57">
-    <cfRule type="cellIs" dxfId="30" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="82" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="29" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B66">
-    <cfRule type="duplicateValues" dxfId="28" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B112">
-    <cfRule type="cellIs" dxfId="27" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="75" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67:B74">
-    <cfRule type="duplicateValues" dxfId="26" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75:B86">
-    <cfRule type="duplicateValues" dxfId="25" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75:B112">
-    <cfRule type="duplicateValues" dxfId="24" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130:B1048576 B113:B124">
-    <cfRule type="duplicateValues" dxfId="22" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C31">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C86">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C126">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C127">
-    <cfRule type="duplicateValues" dxfId="15" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C127:C129">
-    <cfRule type="cellIs" dxfId="12" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="38" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C129">
-    <cfRule type="duplicateValues" dxfId="8" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131">
-    <cfRule type="duplicateValues" dxfId="5" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:K132">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L125:S131">
-    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP125:AU125">
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ128:AQ129">
-    <cfRule type="cellIs" dxfId="0" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
